--- a/Resources/Excel/CelestialNavStars.xlsx
+++ b/Resources/Excel/CelestialNavStars.xlsx
@@ -9,11 +9,16 @@
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="Zfb58/XY0v9Si4EHEP+cmluqqPVptIO+ZPjRcrC76nk="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2122" uniqueCount="1027">
   <si>
     <t>Constellation</t>
   </si>
@@ -1872,36 +1877,42 @@
     <t>10 UMa</t>
   </si>
   <si>
+    <t>Lyra</t>
+  </si>
+  <si>
+    <t>Lyr1</t>
+  </si>
+  <si>
+    <t>Vega</t>
+  </si>
+  <si>
+    <t>Lyr2</t>
+  </si>
+  <si>
+    <t>γ Lyr</t>
+  </si>
+  <si>
+    <t>Lyr3</t>
+  </si>
+  <si>
+    <t>β Lyr A</t>
+  </si>
+  <si>
     <t>Muscae</t>
   </si>
   <si>
+    <t>Mus4</t>
+  </si>
+  <si>
     <t>Mus1</t>
   </si>
   <si>
-    <t>Mus2</t>
-  </si>
-  <si>
-    <t>α Mus</t>
-  </si>
-  <si>
-    <t>Mus3</t>
-  </si>
-  <si>
-    <t>β Mus</t>
+    <t>λ Mus</t>
   </si>
   <si>
     <t>Mus5</t>
   </si>
   <si>
-    <t>δ Mus</t>
-  </si>
-  <si>
-    <t>Mus4</t>
-  </si>
-  <si>
-    <t>λ Mus</t>
-  </si>
-  <si>
     <t>γ Mus</t>
   </si>
   <si>
@@ -2319,7 +2330,7 @@
     <t>ζ Phe</t>
   </si>
   <si>
-    <t>Picis Austrinus</t>
+    <t>Piscis Austrinus</t>
   </si>
   <si>
     <t>Fomalhaut</t>
@@ -3067,27 +3078,6 @@
   </si>
   <si>
     <t>ψ Vel A</t>
-  </si>
-  <si>
-    <t>Vera</t>
-  </si>
-  <si>
-    <t>Ver1</t>
-  </si>
-  <si>
-    <t>Vega</t>
-  </si>
-  <si>
-    <t>Ver2</t>
-  </si>
-  <si>
-    <t>γ Lyr</t>
-  </si>
-  <si>
-    <t>Ver3</t>
-  </si>
-  <si>
-    <t>β Lyr A</t>
   </si>
   <si>
     <t>Virgo</t>
@@ -3151,7 +3141,7 @@
     <numFmt numFmtId="166" formatCode="\+00;\-00;00"/>
     <numFmt numFmtId="167" formatCode="00.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -3161,16 +3151,11 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
@@ -3233,14 +3218,14 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3476,7 +3461,6 @@
     <col customWidth="1" min="12" max="12" width="5.86"/>
     <col customWidth="1" min="13" max="13" width="5.14"/>
     <col customWidth="1" min="14" max="14" width="5.29"/>
-    <col customWidth="1" min="15" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4105,7 +4089,7 @@
       <c r="B18" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>59</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -4149,7 +4133,7 @@
       <c r="E19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -13153,131 +13137,134 @@
       </c>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="1" t="s">
+      <c r="A258" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="B258" s="1" t="s">
+      <c r="B258" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="C258" s="1" t="s">
+      <c r="D258" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="E258" s="1" t="s">
         <v>611</v>
       </c>
       <c r="F258" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H258" s="2">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
       <c r="I258" s="2">
-        <v>37.0</v>
+        <v>36.0</v>
       </c>
       <c r="J258" s="3">
-        <v>11.08</v>
+        <v>56.19</v>
       </c>
       <c r="K258" s="4">
-        <v>-69.0</v>
+        <v>38.0</v>
       </c>
       <c r="L258" s="2">
-        <v>8.0</v>
+        <v>46.0</v>
       </c>
       <c r="M258" s="5">
-        <v>7.9</v>
+        <v>58.8</v>
       </c>
       <c r="N258" s="6">
-        <v>2.69</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="1" t="s">
+      <c r="A259" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="C259" s="1" t="s">
+      <c r="B259" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="C259" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="F259" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="F259" s="7" t="s">
+      <c r="G259" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H259" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="I259" s="2">
+        <v>58.0</v>
+      </c>
+      <c r="J259" s="3">
+        <v>56.62</v>
+      </c>
+      <c r="K259" s="4">
+        <v>32.0</v>
+      </c>
+      <c r="L259" s="2">
+        <v>41.0</v>
+      </c>
+      <c r="M259" s="5">
+        <v>22.4</v>
+      </c>
+      <c r="N259" s="6">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
+      <c r="A260" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="B260" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="G259" s="1" t="s">
+      <c r="C260" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="G260" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H259" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="I259" s="2">
-        <v>46.0</v>
-      </c>
-      <c r="J259" s="3">
-        <v>16.87</v>
-      </c>
-      <c r="K259" s="4">
-        <v>-68.0</v>
-      </c>
-      <c r="L259" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="M259" s="5">
-        <v>29.1</v>
-      </c>
-      <c r="N259" s="6">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="F260" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="G260" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="H260" s="2">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="I260" s="2">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
       <c r="J260" s="3">
-        <v>15.78</v>
+        <v>4.79</v>
       </c>
       <c r="K260" s="4">
-        <v>-71.0</v>
+        <v>33.0</v>
       </c>
       <c r="L260" s="2">
-        <v>32.0</v>
+        <v>21.0</v>
       </c>
       <c r="M260" s="5">
-        <v>55.7</v>
+        <v>45.6</v>
       </c>
       <c r="N260" s="6">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="1" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>617</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="F261" s="7" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>34</v>
@@ -13306,16 +13293,16 @@
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="1" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="F262" s="7" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>24</v>
@@ -13344,22 +13331,22 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D263" s="1">
         <v>46.0</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F263" s="7" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>17</v>
@@ -13388,22 +13375,22 @@
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D264" s="1">
         <v>44.0</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F264" s="7" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>79</v>
@@ -13432,16 +13419,16 @@
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="F265" s="7" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>47</v>
@@ -13470,16 +13457,16 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="F266" s="7" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>26</v>
@@ -13508,16 +13495,16 @@
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F267" s="7" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>21</v>
@@ -13546,16 +13533,16 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="F268" s="7" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>162</v>
@@ -13584,16 +13571,16 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F269" s="7" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>55</v>
@@ -13622,13 +13609,13 @@
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="F270" s="7" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>72</v>
@@ -13657,16 +13644,16 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="F271" s="7" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>121</v>
@@ -13695,13 +13682,13 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F272" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H272" s="2">
         <v>18.0</v>
@@ -13727,16 +13714,16 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F273" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>24</v>
@@ -13765,16 +13752,16 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="F274" s="7" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>34</v>
@@ -13803,13 +13790,13 @@
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F275" s="7" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H275" s="2">
         <v>18.0</v>
@@ -13835,22 +13822,22 @@
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D276" s="1">
         <v>11.0</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F276" s="7" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>21</v>
@@ -13879,22 +13866,22 @@
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D277" s="1">
         <v>16.0</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F277" s="7" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>17</v>
@@ -13923,22 +13910,22 @@
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D278" s="1">
         <v>13.0</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F278" s="7" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>24</v>
@@ -13967,19 +13954,19 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D279" s="1">
         <v>15.0</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F279" s="7" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>55</v>
@@ -14008,16 +13995,16 @@
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F280" s="7" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>47</v>
@@ -14046,16 +14033,16 @@
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F281" s="7" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>162</v>
@@ -14084,16 +14071,16 @@
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F282" s="7" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>26</v>
@@ -14122,13 +14109,13 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="F283" s="7" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>113</v>
@@ -14157,13 +14144,13 @@
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F284" s="7" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>250</v>
@@ -14192,16 +14179,16 @@
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F285" s="7" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>79</v>
@@ -14230,16 +14217,16 @@
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F286" s="7" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>34</v>
@@ -14268,16 +14255,16 @@
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>281</v>
@@ -14306,13 +14293,13 @@
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F288" s="7" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="H288" s="2">
         <v>4.0</v>
@@ -14338,13 +14325,13 @@
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F289" s="7" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>47</v>
@@ -14373,13 +14360,13 @@
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F290" s="7" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H290" s="2">
         <v>4.0</v>
@@ -14405,22 +14392,22 @@
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D291" s="1">
         <v>52.0</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="F291" s="7" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>17</v>
@@ -14449,13 +14436,13 @@
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="F292" s="7" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>21</v>
@@ -14484,16 +14471,16 @@
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="F293" s="7" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>26</v>
@@ -14522,16 +14509,16 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F294" s="7" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>79</v>
@@ -14560,16 +14547,16 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F295" s="7" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>55</v>
@@ -14598,22 +14585,22 @@
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D296" s="1">
         <v>54.0</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F296" s="7" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>55</v>
@@ -14642,16 +14629,16 @@
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F297" s="7" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>21</v>
@@ -14680,22 +14667,22 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B298" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C298" s="1" t="s">
         <v>699</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>697</v>
       </c>
       <c r="D298" s="1">
         <v>57.0</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F298" s="7" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>17</v>
@@ -14724,16 +14711,16 @@
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F299" s="7" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>24</v>
@@ -14762,16 +14749,16 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="F300" s="7" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>79</v>
@@ -14800,16 +14787,16 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F301" s="7" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G301" s="1" t="s">
         <v>47</v>
@@ -14838,16 +14825,16 @@
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="F302" s="7" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G302" s="1" t="s">
         <v>37</v>
@@ -14876,16 +14863,16 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="F303" s="7" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G303" s="1" t="s">
         <v>72</v>
@@ -14914,16 +14901,16 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F304" s="7" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>113</v>
@@ -14952,22 +14939,22 @@
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D305" s="1">
         <v>9.0</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="F305" s="7" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G305" s="1" t="s">
         <v>17</v>
@@ -14996,16 +14983,16 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="F306" s="7" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G306" s="1" t="s">
         <v>21</v>
@@ -15034,16 +15021,16 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F307" s="7" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G307" s="1" t="s">
         <v>47</v>
@@ -15072,16 +15059,16 @@
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="F308" s="7" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G308" s="1" t="s">
         <v>55</v>
@@ -15110,16 +15097,16 @@
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="F309" s="7" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G309" s="1" t="s">
         <v>24</v>
@@ -15148,16 +15135,16 @@
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="F310" s="7" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G310" s="1" t="s">
         <v>26</v>
@@ -15186,13 +15173,13 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="F311" s="7" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>138</v>
@@ -15221,13 +15208,13 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="F312" s="7" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G312" s="1" t="s">
         <v>79</v>
@@ -15256,13 +15243,13 @@
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="F313" s="7" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G313" s="1" t="s">
         <v>121</v>
@@ -15291,16 +15278,16 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="F314" s="7" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="G314" s="1" t="s">
         <v>162</v>
@@ -15329,13 +15316,13 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="F315" s="7" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>31</v>
@@ -15364,13 +15351,13 @@
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="F316" s="7" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>281</v>
@@ -15399,13 +15386,13 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F317" s="7" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>50</v>
@@ -15434,16 +15421,16 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="F318" s="7" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>383</v>
@@ -15472,22 +15459,22 @@
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D319" s="1">
         <v>2.0</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="F319" s="7" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>17</v>
@@ -15516,16 +15503,16 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F320" s="7" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>21</v>
@@ -15554,16 +15541,16 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B321" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C321" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="C321" s="1" t="s">
-        <v>747</v>
-      </c>
       <c r="F321" s="7" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>24</v>
@@ -15592,13 +15579,13 @@
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F322" s="7" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>55</v>
@@ -15627,13 +15614,13 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>162</v>
@@ -15662,13 +15649,13 @@
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>26</v>
@@ -15697,13 +15684,13 @@
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>47</v>
@@ -15731,17 +15718,17 @@
       </c>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="1" t="s">
-        <v>758</v>
+      <c r="A326" s="8" t="s">
+        <v>760</v>
       </c>
       <c r="D326" s="1">
         <v>56.0</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>17</v>
@@ -15770,16 +15757,16 @@
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="G327" s="1" t="s">
         <v>47</v>
@@ -15808,16 +15795,16 @@
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>250</v>
@@ -15846,16 +15833,16 @@
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>138</v>
@@ -15884,16 +15871,16 @@
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>281</v>
@@ -15922,13 +15909,13 @@
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="G331" s="1" t="s">
         <v>121</v>
@@ -15957,16 +15944,16 @@
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>571</v>
@@ -15995,16 +15982,16 @@
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="F333" s="7" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>383</v>
@@ -16033,13 +16020,13 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="F334" s="7" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>50</v>
@@ -16068,16 +16055,16 @@
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F335" s="7" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="H335" s="2">
         <v>7.0</v>
@@ -16103,16 +16090,16 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="1" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="F336" s="7" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="H336" s="2">
         <v>7.0</v>
@@ -16138,22 +16125,22 @@
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D337" s="1">
         <v>48.0</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="F337" s="7" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>55</v>
@@ -16182,19 +16169,19 @@
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D338" s="1">
         <v>50.0</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="F338" s="7" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="G338" s="1" t="s">
         <v>571</v>
@@ -16223,16 +16210,16 @@
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F339" s="7" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="G339" s="1" t="s">
         <v>47</v>
@@ -16261,16 +16248,16 @@
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="F340" s="7" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="G340" s="1" t="s">
         <v>26</v>
@@ -16299,16 +16286,16 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F341" s="7" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="G341" s="1" t="s">
         <v>34</v>
@@ -16337,16 +16324,16 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F342" s="7" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G342" s="1" t="s">
         <v>250</v>
@@ -16375,16 +16362,16 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="F343" s="7" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="G343" s="1" t="s">
         <v>24</v>
@@ -16413,13 +16400,13 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F344" s="7" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="G344" s="1" t="s">
         <v>79</v>
@@ -16448,16 +16435,16 @@
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F345" s="7" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G345" s="1" t="s">
         <v>248</v>
@@ -16486,13 +16473,13 @@
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F346" s="7" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="G346" s="1" t="s">
         <v>281</v>
@@ -16521,13 +16508,13 @@
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F347" s="7" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="G347" s="1" t="s">
         <v>383</v>
@@ -16556,13 +16543,13 @@
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="F348" s="7" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="G348" s="1" t="s">
         <v>37</v>
@@ -16591,13 +16578,13 @@
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F349" s="7" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="G349" s="1" t="s">
         <v>138</v>
@@ -16626,13 +16613,13 @@
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F350" s="7" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="G350" s="1" t="s">
         <v>21</v>
@@ -16661,13 +16648,13 @@
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="1" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="F351" s="7" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="G351" s="1" t="s">
         <v>17</v>
@@ -16696,22 +16683,22 @@
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D352" s="1">
         <v>42.0</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F352" s="7" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="G352" s="1" t="s">
         <v>17</v>
@@ -16740,22 +16727,22 @@
     </row>
     <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D353" s="1">
         <v>45.0</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F353" s="7" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>34</v>
@@ -16784,16 +16771,16 @@
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="F354" s="7" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="G354" s="1" t="s">
         <v>72</v>
@@ -16822,16 +16809,16 @@
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F355" s="7" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>26</v>
@@ -16860,16 +16847,16 @@
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F356" s="7" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="G356" s="1" t="s">
         <v>55</v>
@@ -16898,16 +16885,16 @@
     </row>
     <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="F357" s="7" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G357" s="1" t="s">
         <v>162</v>
@@ -16936,13 +16923,13 @@
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F358" s="7" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="G358" s="1" t="s">
         <v>21</v>
@@ -16971,16 +16958,16 @@
     </row>
     <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F359" s="7" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="G359" s="1" t="s">
         <v>281</v>
@@ -17009,16 +16996,16 @@
     </row>
     <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F360" s="7" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G360" s="1" t="s">
         <v>250</v>
@@ -17047,16 +17034,16 @@
     </row>
     <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F361" s="7" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="G361" s="1" t="s">
         <v>571</v>
@@ -17085,16 +17072,16 @@
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="F362" s="7" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="G362" s="1" t="s">
         <v>113</v>
@@ -17123,16 +17110,16 @@
     </row>
     <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F363" s="7" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="G363" s="1" t="s">
         <v>37</v>
@@ -17161,16 +17148,16 @@
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="F364" s="7" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H364" s="2">
         <v>17.0</v>
@@ -17196,16 +17183,16 @@
     </row>
     <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="F365" s="7" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="G365" s="1" t="s">
         <v>79</v>
@@ -17234,16 +17221,16 @@
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="F366" s="7" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>47</v>
@@ -17272,16 +17259,16 @@
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="F367" s="7" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="G367" s="1" t="s">
         <v>138</v>
@@ -17310,16 +17297,16 @@
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>17</v>
@@ -17348,13 +17335,13 @@
     </row>
     <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="G369" s="1" t="s">
         <v>79</v>
@@ -17383,16 +17370,16 @@
     </row>
     <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>37</v>
@@ -17421,13 +17408,13 @@
     </row>
     <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G371" s="1" t="s">
         <v>383</v>
@@ -17456,13 +17443,13 @@
     </row>
     <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>21</v>
@@ -17491,16 +17478,16 @@
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="G373" s="1" t="s">
         <v>55</v>
@@ -17529,16 +17516,16 @@
     </row>
     <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="G374" s="1" t="s">
         <v>26</v>
@@ -17567,22 +17554,22 @@
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D375" s="1">
         <v>10.0</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F375" s="7" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G375" s="1" t="s">
         <v>17</v>
@@ -17611,22 +17598,22 @@
     </row>
     <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D376" s="1">
         <v>14.0</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="F376" s="7" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>21</v>
@@ -17655,13 +17642,13 @@
     </row>
     <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="F377" s="7" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>79</v>
@@ -17690,13 +17677,13 @@
     </row>
     <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="F378" s="7" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>47</v>
@@ -17725,16 +17712,16 @@
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="F379" s="7" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="G379" s="1" t="s">
         <v>72</v>
@@ -17763,16 +17750,16 @@
     </row>
     <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="F380" s="7" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>34</v>
@@ -17801,16 +17788,16 @@
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F381" s="7" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>55</v>
@@ -17839,13 +17826,13 @@
     </row>
     <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F382" s="7" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>31</v>
@@ -17874,16 +17861,16 @@
     </row>
     <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="F383" s="7" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="G383" s="1" t="s">
         <v>24</v>
@@ -17912,16 +17899,16 @@
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="F384" s="7" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>383</v>
@@ -17950,16 +17937,16 @@
     </row>
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B385" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="C385" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="C385" s="1" t="s">
-        <v>881</v>
-      </c>
       <c r="F385" s="7" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>26</v>
@@ -17988,13 +17975,13 @@
     </row>
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F386" s="7" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="H386" s="2">
         <v>3.0</v>
@@ -18020,13 +18007,13 @@
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="1" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="F387" s="7" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>121</v>
@@ -18055,16 +18042,16 @@
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="F388" s="7" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>21</v>
@@ -18093,16 +18080,16 @@
     </row>
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="F389" s="7" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>17</v>
@@ -18131,16 +18118,16 @@
     </row>
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F390" s="9" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G390" s="10" t="s">
         <v>24</v>
@@ -18169,22 +18156,22 @@
     </row>
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="1" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D391" s="1">
         <v>43.0</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="F391" s="7" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>17</v>
@@ -18213,16 +18200,16 @@
     </row>
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="1" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="F392" s="7" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>21</v>
@@ -18251,16 +18238,16 @@
     </row>
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="1" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="F393" s="7" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="G393" s="1" t="s">
         <v>24</v>
@@ -18289,13 +18276,13 @@
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="1" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="F394" s="7" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="G394" s="1" t="s">
         <v>26</v>
@@ -18324,16 +18311,16 @@
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="1" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="F395" s="7" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="G395" s="1" t="s">
         <v>17</v>
@@ -18362,13 +18349,13 @@
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="1" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="F396" s="7" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="G396" s="1" t="s">
         <v>24</v>
@@ -18397,22 +18384,22 @@
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D397" s="1">
         <v>32.0</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="F397" s="7" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>55</v>
@@ -18441,22 +18428,22 @@
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D398" s="1">
         <v>27.0</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="F398" s="7" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="G398" s="1" t="s">
         <v>17</v>
@@ -18485,22 +18472,22 @@
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D399" s="1">
         <v>34.0</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="F399" s="7" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G399" s="1" t="s">
         <v>79</v>
@@ -18529,16 +18516,16 @@
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="F400" s="7" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="G400" s="1" t="s">
         <v>47</v>
@@ -18567,16 +18554,16 @@
     </row>
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="F401" s="7" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="G401" s="1" t="s">
         <v>21</v>
@@ -18605,16 +18592,16 @@
     </row>
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="F402" s="7" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="G402" s="1" t="s">
         <v>24</v>
@@ -18643,19 +18630,19 @@
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="F403" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="G403" s="1" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="H403" s="2">
         <v>11.0</v>
@@ -18681,16 +18668,16 @@
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="F404" s="7" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="G404" s="1" t="s">
         <v>37</v>
@@ -18719,16 +18706,16 @@
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="F405" s="7" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="G405" s="1" t="s">
         <v>113</v>
@@ -18757,16 +18744,16 @@
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="F406" s="7" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>72</v>
@@ -18795,16 +18782,16 @@
     </row>
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="F407" s="7" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="G407" s="1" t="s">
         <v>26</v>
@@ -18833,13 +18820,13 @@
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="F408" s="7" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>31</v>
@@ -18868,16 +18855,16 @@
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="F409" s="7" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="G409" s="1" t="s">
         <v>34</v>
@@ -18906,16 +18893,16 @@
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="F410" s="7" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="G410" s="1" t="s">
         <v>121</v>
@@ -18944,16 +18931,16 @@
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="H411" s="2">
         <v>9.0</v>
@@ -18979,16 +18966,16 @@
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="F412" s="7" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>202</v>
@@ -19017,13 +19004,13 @@
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F413" s="7" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="G413" s="1" t="s">
         <v>197</v>
@@ -19052,16 +19039,16 @@
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="1" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="F414" s="7" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>383</v>
@@ -19090,16 +19077,16 @@
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="1" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="F415" s="7" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>17</v>
@@ -19128,22 +19115,22 @@
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="1" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="D416" s="1">
         <v>40.0</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="F416" s="7" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>21</v>
@@ -19172,16 +19159,16 @@
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="1" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="F417" s="7" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>24</v>
@@ -19210,16 +19197,16 @@
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="1" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="F418" s="9" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="G418" s="11" t="s">
         <v>55</v>
@@ -19248,16 +19235,16 @@
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="1" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="F419" s="9" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="G419" s="11" t="s">
         <v>47</v>
@@ -19286,16 +19273,16 @@
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="1" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="F420" s="9" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="G420" s="11" t="s">
         <v>26</v>
@@ -19324,16 +19311,16 @@
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="1" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="F421" s="9" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="G421" s="10" t="s">
         <v>79</v>
@@ -19362,22 +19349,22 @@
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D422" s="1">
         <v>23.0</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="F422" s="7" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>24</v>
@@ -19406,16 +19393,16 @@
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="F423" s="7" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="G423" s="1" t="s">
         <v>26</v>
@@ -19444,16 +19431,16 @@
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="F424" s="7" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>34</v>
@@ -19482,13 +19469,13 @@
     </row>
     <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="F425" s="7" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>162</v>
@@ -19517,16 +19504,16 @@
     </row>
     <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F426" s="7" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>37</v>
@@ -19555,19 +19542,19 @@
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="F427" s="7" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="H427" s="2">
         <v>9.0</v>
@@ -19593,16 +19580,16 @@
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="F428" s="7" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>248</v>
@@ -19631,16 +19618,16 @@
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="F429" s="7" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>31</v>
@@ -19669,13 +19656,13 @@
     </row>
     <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="F430" s="7" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="G430" s="1" t="s">
         <v>50</v>
@@ -19704,13 +19691,13 @@
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F431" s="7" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>60</v>
@@ -19739,16 +19726,16 @@
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="F432" s="7" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="H432" s="2">
         <v>10.0</v>
@@ -19774,19 +19761,19 @@
     </row>
     <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F433" s="7" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="H433" s="2">
         <v>10.0</v>
@@ -19812,16 +19799,16 @@
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="F434" s="7" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="H434" s="2">
         <v>8.0</v>
@@ -19847,19 +19834,19 @@
     </row>
     <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="1" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F435" s="7" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="H435" s="2">
         <v>9.0</v>
@@ -19885,418 +19872,328 @@
     </row>
     <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="1" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>1009</v>
+        <v>1011</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>1012</v>
       </c>
       <c r="D436" s="1">
-        <v>49.0</v>
+        <v>33.0</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="F436" s="7" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H436" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="I436" s="2">
-        <v>36.0</v>
+        <v>25.0</v>
       </c>
       <c r="J436" s="3">
-        <v>56.19</v>
+        <v>11.6</v>
       </c>
       <c r="K436" s="4">
-        <v>38.0</v>
+        <v>-11.0</v>
       </c>
       <c r="L436" s="2">
-        <v>46.0</v>
+        <v>9.0</v>
       </c>
       <c r="M436" s="5">
-        <v>58.8</v>
+        <v>40.5</v>
       </c>
       <c r="N436" s="6">
-        <v>0.03</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="1" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>1009</v>
+        <v>1014</v>
       </c>
       <c r="F437" s="7" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="G437" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H437" s="2">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="I437" s="2">
-        <v>58.0</v>
+        <v>41.0</v>
       </c>
       <c r="J437" s="3">
-        <v>56.62</v>
+        <v>40.0</v>
       </c>
       <c r="K437" s="4">
-        <v>32.0</v>
+        <v>-1.0</v>
       </c>
       <c r="L437" s="2">
-        <v>41.0</v>
+        <v>26.0</v>
       </c>
       <c r="M437" s="5">
-        <v>22.4</v>
+        <v>58.3</v>
       </c>
       <c r="N437" s="6">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="1" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="F438" s="7" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="H438" s="2">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="I438" s="2">
-        <v>50.0</v>
+        <v>2.0</v>
       </c>
       <c r="J438" s="3">
-        <v>4.79</v>
+        <v>10.76</v>
       </c>
       <c r="K438" s="4">
-        <v>33.0</v>
+        <v>10.0</v>
       </c>
       <c r="L438" s="2">
-        <v>21.0</v>
+        <v>57.0</v>
       </c>
       <c r="M438" s="5">
-        <v>45.6</v>
+        <v>32.8</v>
       </c>
       <c r="N438" s="6">
-        <v>3.52</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="1" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C439" s="1" t="s">
         <v>1017</v>
       </c>
-      <c r="D439" s="1">
-        <v>33.0</v>
-      </c>
-      <c r="E439" s="1" t="s">
-        <v>1018</v>
-      </c>
       <c r="F439" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H439" s="2">
         <v>13.0</v>
       </c>
       <c r="I439" s="2">
-        <v>25.0</v>
+        <v>34.0</v>
       </c>
       <c r="J439" s="3">
-        <v>11.6</v>
+        <v>41.75</v>
       </c>
       <c r="K439" s="4">
-        <v>-11.0</v>
+        <v>0.0</v>
       </c>
       <c r="L439" s="2">
-        <v>9.0</v>
+        <v>35.0</v>
       </c>
       <c r="M439" s="5">
-        <v>40.5</v>
+        <v>45.4</v>
       </c>
       <c r="N439" s="6">
-        <v>0.98</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="1" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="F440" s="7" t="s">
         <v>1020</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H440" s="2">
         <v>12.0</v>
       </c>
       <c r="I440" s="2">
-        <v>41.0</v>
+        <v>55.0</v>
       </c>
       <c r="J440" s="3">
-        <v>40.0</v>
+        <v>36.48</v>
       </c>
       <c r="K440" s="4">
-        <v>-1.0</v>
+        <v>3.0</v>
       </c>
       <c r="L440" s="2">
-        <v>26.0</v>
+        <v>23.0</v>
       </c>
       <c r="M440" s="5">
-        <v>58.3</v>
+        <v>51.4</v>
       </c>
       <c r="N440" s="6">
-        <v>2.74</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="1" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="B441" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="C441" s="1" t="s">
+      <c r="F441" s="7" t="s">
         <v>1022</v>
       </c>
-      <c r="F441" s="7" t="s">
-        <v>1023</v>
-      </c>
       <c r="G441" s="1" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="H441" s="2">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="I441" s="2">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
       <c r="J441" s="3">
-        <v>10.76</v>
+        <v>41.29</v>
       </c>
       <c r="K441" s="4">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="L441" s="2">
-        <v>57.0</v>
+        <v>45.0</v>
       </c>
       <c r="M441" s="5">
-        <v>32.8</v>
+        <v>55.4</v>
       </c>
       <c r="N441" s="6">
-        <v>2.85</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="1" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F442" s="7" t="s">
         <v>1024</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H442" s="2">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="I442" s="2">
-        <v>34.0</v>
+        <v>43.0</v>
       </c>
       <c r="J442" s="3">
-        <v>41.75</v>
+        <v>3.56</v>
       </c>
       <c r="K442" s="4">
-        <v>0.0</v>
+        <v>-5.0</v>
       </c>
       <c r="L442" s="2">
-        <v>35.0</v>
+        <v>39.0</v>
       </c>
       <c r="M442" s="5">
-        <v>45.4</v>
+        <v>26.7</v>
       </c>
       <c r="N442" s="6">
-        <v>3.38</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="1" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C443" s="1" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F443" s="7" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="H443" s="2">
         <v>12.0</v>
       </c>
       <c r="I443" s="2">
-        <v>55.0</v>
+        <v>19.0</v>
       </c>
       <c r="J443" s="3">
-        <v>36.48</v>
+        <v>54.39</v>
       </c>
       <c r="K443" s="4">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L443" s="2">
-        <v>23.0</v>
+        <v>40.0</v>
       </c>
       <c r="M443" s="5">
-        <v>51.4</v>
+        <v>0.3</v>
       </c>
       <c r="N443" s="6">
-        <v>3.39</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B444" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F444" s="7" t="s">
-        <v>1027</v>
-      </c>
-      <c r="G444" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H444" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="I444" s="2">
-        <v>50.0</v>
-      </c>
-      <c r="J444" s="3">
-        <v>41.29</v>
-      </c>
-      <c r="K444" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="L444" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="M444" s="5">
-        <v>55.4</v>
-      </c>
-      <c r="N444" s="6">
-        <v>3.59</v>
-      </c>
+      <c r="H444" s="2"/>
+      <c r="I444" s="2"/>
+      <c r="J444" s="3"/>
+      <c r="K444" s="4"/>
+      <c r="L444" s="2"/>
+      <c r="M444" s="5"/>
+      <c r="N444" s="6"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B445" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F445" s="7" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G445" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H445" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="I445" s="2">
-        <v>43.0</v>
-      </c>
-      <c r="J445" s="3">
-        <v>3.56</v>
-      </c>
-      <c r="K445" s="4">
-        <v>-5.0</v>
-      </c>
-      <c r="L445" s="2">
-        <v>39.0</v>
-      </c>
-      <c r="M445" s="5">
-        <v>26.7</v>
-      </c>
-      <c r="N445" s="6">
-        <v>3.87</v>
-      </c>
+      <c r="H445" s="2"/>
+      <c r="I445" s="2"/>
+      <c r="J445" s="3"/>
+      <c r="K445" s="4"/>
+      <c r="L445" s="2"/>
+      <c r="M445" s="5"/>
+      <c r="N445" s="6"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B446" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F446" s="7" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G446" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H446" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="I446" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="J446" s="3">
-        <v>54.39</v>
-      </c>
-      <c r="K446" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="L446" s="2">
-        <v>40.0</v>
-      </c>
-      <c r="M446" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="N446" s="6">
-        <v>3.89</v>
-      </c>
+      <c r="H446" s="2"/>
+      <c r="I446" s="2"/>
+      <c r="J446" s="3"/>
+      <c r="K446" s="4"/>
+      <c r="L446" s="2"/>
+      <c r="M446" s="5"/>
+      <c r="N446" s="6"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="H447" s="2"/>
@@ -22071,3219 +21968,360 @@
       <c r="M643" s="5"/>
       <c r="N643" s="6"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
-      <c r="H644" s="2"/>
-      <c r="I644" s="2"/>
-      <c r="J644" s="3"/>
-      <c r="K644" s="4"/>
-      <c r="L644" s="2"/>
-      <c r="M644" s="5"/>
-      <c r="N644" s="6"/>
-    </row>
-    <row r="645" ht="15.75" customHeight="1">
-      <c r="H645" s="2"/>
-      <c r="I645" s="2"/>
-      <c r="J645" s="3"/>
-      <c r="K645" s="4"/>
-      <c r="L645" s="2"/>
-      <c r="M645" s="5"/>
-      <c r="N645" s="6"/>
-    </row>
-    <row r="646" ht="15.75" customHeight="1">
-      <c r="H646" s="2"/>
-      <c r="I646" s="2"/>
-      <c r="J646" s="3"/>
-      <c r="K646" s="4"/>
-      <c r="L646" s="2"/>
-      <c r="M646" s="5"/>
-      <c r="N646" s="6"/>
-    </row>
-    <row r="647" ht="15.75" customHeight="1">
-      <c r="H647" s="2"/>
-      <c r="I647" s="2"/>
-      <c r="J647" s="3"/>
-      <c r="K647" s="4"/>
-      <c r="L647" s="2"/>
-      <c r="M647" s="5"/>
-      <c r="N647" s="6"/>
-    </row>
-    <row r="648" ht="15.75" customHeight="1">
-      <c r="H648" s="2"/>
-      <c r="I648" s="2"/>
-      <c r="J648" s="3"/>
-      <c r="K648" s="4"/>
-      <c r="L648" s="2"/>
-      <c r="M648" s="5"/>
-      <c r="N648" s="6"/>
-    </row>
-    <row r="649" ht="15.75" customHeight="1">
-      <c r="H649" s="2"/>
-      <c r="I649" s="2"/>
-      <c r="J649" s="3"/>
-      <c r="K649" s="4"/>
-      <c r="L649" s="2"/>
-      <c r="M649" s="5"/>
-      <c r="N649" s="6"/>
-    </row>
-    <row r="650" ht="15.75" customHeight="1">
-      <c r="H650" s="2"/>
-      <c r="I650" s="2"/>
-      <c r="J650" s="3"/>
-      <c r="K650" s="4"/>
-      <c r="L650" s="2"/>
-      <c r="M650" s="5"/>
-      <c r="N650" s="6"/>
-    </row>
-    <row r="651" ht="15.75" customHeight="1">
-      <c r="H651" s="2"/>
-      <c r="I651" s="2"/>
-      <c r="J651" s="3"/>
-      <c r="K651" s="4"/>
-      <c r="L651" s="2"/>
-      <c r="M651" s="5"/>
-      <c r="N651" s="6"/>
-    </row>
-    <row r="652" ht="15.75" customHeight="1">
-      <c r="H652" s="2"/>
-      <c r="I652" s="2"/>
-      <c r="J652" s="3"/>
-      <c r="K652" s="4"/>
-      <c r="L652" s="2"/>
-      <c r="M652" s="5"/>
-      <c r="N652" s="6"/>
-    </row>
-    <row r="653" ht="15.75" customHeight="1">
-      <c r="H653" s="2"/>
-      <c r="I653" s="2"/>
-      <c r="J653" s="3"/>
-      <c r="K653" s="4"/>
-      <c r="L653" s="2"/>
-      <c r="M653" s="5"/>
-      <c r="N653" s="6"/>
-    </row>
-    <row r="654" ht="15.75" customHeight="1">
-      <c r="H654" s="2"/>
-      <c r="I654" s="2"/>
-      <c r="J654" s="3"/>
-      <c r="K654" s="4"/>
-      <c r="L654" s="2"/>
-      <c r="M654" s="5"/>
-      <c r="N654" s="6"/>
-    </row>
-    <row r="655" ht="15.75" customHeight="1">
-      <c r="H655" s="2"/>
-      <c r="I655" s="2"/>
-      <c r="J655" s="3"/>
-      <c r="K655" s="4"/>
-      <c r="L655" s="2"/>
-      <c r="M655" s="5"/>
-      <c r="N655" s="6"/>
-    </row>
-    <row r="656" ht="15.75" customHeight="1">
-      <c r="H656" s="2"/>
-      <c r="I656" s="2"/>
-      <c r="J656" s="3"/>
-      <c r="K656" s="4"/>
-      <c r="L656" s="2"/>
-      <c r="M656" s="5"/>
-      <c r="N656" s="6"/>
-    </row>
-    <row r="657" ht="15.75" customHeight="1">
-      <c r="H657" s="2"/>
-      <c r="I657" s="2"/>
-      <c r="J657" s="3"/>
-      <c r="K657" s="4"/>
-      <c r="L657" s="2"/>
-      <c r="M657" s="5"/>
-      <c r="N657" s="6"/>
-    </row>
-    <row r="658" ht="15.75" customHeight="1">
-      <c r="H658" s="2"/>
-      <c r="I658" s="2"/>
-      <c r="J658" s="3"/>
-      <c r="K658" s="4"/>
-      <c r="L658" s="2"/>
-      <c r="M658" s="5"/>
-      <c r="N658" s="6"/>
-    </row>
-    <row r="659" ht="15.75" customHeight="1">
-      <c r="H659" s="2"/>
-      <c r="I659" s="2"/>
-      <c r="J659" s="3"/>
-      <c r="K659" s="4"/>
-      <c r="L659" s="2"/>
-      <c r="M659" s="5"/>
-      <c r="N659" s="6"/>
-    </row>
-    <row r="660" ht="15.75" customHeight="1">
-      <c r="H660" s="2"/>
-      <c r="I660" s="2"/>
-      <c r="J660" s="3"/>
-      <c r="K660" s="4"/>
-      <c r="L660" s="2"/>
-      <c r="M660" s="5"/>
-      <c r="N660" s="6"/>
-    </row>
-    <row r="661" ht="15.75" customHeight="1">
-      <c r="H661" s="2"/>
-      <c r="I661" s="2"/>
-      <c r="J661" s="3"/>
-      <c r="K661" s="4"/>
-      <c r="L661" s="2"/>
-      <c r="M661" s="5"/>
-      <c r="N661" s="6"/>
-    </row>
-    <row r="662" ht="15.75" customHeight="1">
-      <c r="H662" s="2"/>
-      <c r="I662" s="2"/>
-      <c r="J662" s="3"/>
-      <c r="K662" s="4"/>
-      <c r="L662" s="2"/>
-      <c r="M662" s="5"/>
-      <c r="N662" s="6"/>
-    </row>
-    <row r="663" ht="15.75" customHeight="1">
-      <c r="H663" s="2"/>
-      <c r="I663" s="2"/>
-      <c r="J663" s="3"/>
-      <c r="K663" s="4"/>
-      <c r="L663" s="2"/>
-      <c r="M663" s="5"/>
-      <c r="N663" s="6"/>
-    </row>
-    <row r="664" ht="15.75" customHeight="1">
-      <c r="H664" s="2"/>
-      <c r="I664" s="2"/>
-      <c r="J664" s="3"/>
-      <c r="K664" s="4"/>
-      <c r="L664" s="2"/>
-      <c r="M664" s="5"/>
-      <c r="N664" s="6"/>
-    </row>
-    <row r="665" ht="15.75" customHeight="1">
-      <c r="H665" s="2"/>
-      <c r="I665" s="2"/>
-      <c r="J665" s="3"/>
-      <c r="K665" s="4"/>
-      <c r="L665" s="2"/>
-      <c r="M665" s="5"/>
-      <c r="N665" s="6"/>
-    </row>
-    <row r="666" ht="15.75" customHeight="1">
-      <c r="H666" s="2"/>
-      <c r="I666" s="2"/>
-      <c r="J666" s="3"/>
-      <c r="K666" s="4"/>
-      <c r="L666" s="2"/>
-      <c r="M666" s="5"/>
-      <c r="N666" s="6"/>
-    </row>
-    <row r="667" ht="15.75" customHeight="1">
-      <c r="H667" s="2"/>
-      <c r="I667" s="2"/>
-      <c r="J667" s="3"/>
-      <c r="K667" s="4"/>
-      <c r="L667" s="2"/>
-      <c r="M667" s="5"/>
-      <c r="N667" s="6"/>
-    </row>
-    <row r="668" ht="15.75" customHeight="1">
-      <c r="H668" s="2"/>
-      <c r="I668" s="2"/>
-      <c r="J668" s="3"/>
-      <c r="K668" s="4"/>
-      <c r="L668" s="2"/>
-      <c r="M668" s="5"/>
-      <c r="N668" s="6"/>
-    </row>
-    <row r="669" ht="15.75" customHeight="1">
-      <c r="H669" s="2"/>
-      <c r="I669" s="2"/>
-      <c r="J669" s="3"/>
-      <c r="K669" s="4"/>
-      <c r="L669" s="2"/>
-      <c r="M669" s="5"/>
-      <c r="N669" s="6"/>
-    </row>
-    <row r="670" ht="15.75" customHeight="1">
-      <c r="H670" s="2"/>
-      <c r="I670" s="2"/>
-      <c r="J670" s="3"/>
-      <c r="K670" s="4"/>
-      <c r="L670" s="2"/>
-      <c r="M670" s="5"/>
-      <c r="N670" s="6"/>
-    </row>
-    <row r="671" ht="15.75" customHeight="1">
-      <c r="H671" s="2"/>
-      <c r="I671" s="2"/>
-      <c r="J671" s="3"/>
-      <c r="K671" s="4"/>
-      <c r="L671" s="2"/>
-      <c r="M671" s="5"/>
-      <c r="N671" s="6"/>
-    </row>
-    <row r="672" ht="15.75" customHeight="1">
-      <c r="H672" s="2"/>
-      <c r="I672" s="2"/>
-      <c r="J672" s="3"/>
-      <c r="K672" s="4"/>
-      <c r="L672" s="2"/>
-      <c r="M672" s="5"/>
-      <c r="N672" s="6"/>
-    </row>
-    <row r="673" ht="15.75" customHeight="1">
-      <c r="H673" s="2"/>
-      <c r="I673" s="2"/>
-      <c r="J673" s="3"/>
-      <c r="K673" s="4"/>
-      <c r="L673" s="2"/>
-      <c r="M673" s="5"/>
-      <c r="N673" s="6"/>
-    </row>
-    <row r="674" ht="15.75" customHeight="1">
-      <c r="H674" s="2"/>
-      <c r="I674" s="2"/>
-      <c r="J674" s="3"/>
-      <c r="K674" s="4"/>
-      <c r="L674" s="2"/>
-      <c r="M674" s="5"/>
-      <c r="N674" s="6"/>
-    </row>
-    <row r="675" ht="15.75" customHeight="1">
-      <c r="H675" s="2"/>
-      <c r="I675" s="2"/>
-      <c r="J675" s="3"/>
-      <c r="K675" s="4"/>
-      <c r="L675" s="2"/>
-      <c r="M675" s="5"/>
-      <c r="N675" s="6"/>
-    </row>
-    <row r="676" ht="15.75" customHeight="1">
-      <c r="H676" s="2"/>
-      <c r="I676" s="2"/>
-      <c r="J676" s="3"/>
-      <c r="K676" s="4"/>
-      <c r="L676" s="2"/>
-      <c r="M676" s="5"/>
-      <c r="N676" s="6"/>
-    </row>
-    <row r="677" ht="15.75" customHeight="1">
-      <c r="H677" s="2"/>
-      <c r="I677" s="2"/>
-      <c r="J677" s="3"/>
-      <c r="K677" s="4"/>
-      <c r="L677" s="2"/>
-      <c r="M677" s="5"/>
-      <c r="N677" s="6"/>
-    </row>
-    <row r="678" ht="15.75" customHeight="1">
-      <c r="H678" s="2"/>
-      <c r="I678" s="2"/>
-      <c r="J678" s="3"/>
-      <c r="K678" s="4"/>
-      <c r="L678" s="2"/>
-      <c r="M678" s="5"/>
-      <c r="N678" s="6"/>
-    </row>
-    <row r="679" ht="15.75" customHeight="1">
-      <c r="H679" s="2"/>
-      <c r="I679" s="2"/>
-      <c r="J679" s="3"/>
-      <c r="K679" s="4"/>
-      <c r="L679" s="2"/>
-      <c r="M679" s="5"/>
-      <c r="N679" s="6"/>
-    </row>
-    <row r="680" ht="15.75" customHeight="1">
-      <c r="H680" s="2"/>
-      <c r="I680" s="2"/>
-      <c r="J680" s="3"/>
-      <c r="K680" s="4"/>
-      <c r="L680" s="2"/>
-      <c r="M680" s="5"/>
-      <c r="N680" s="6"/>
-    </row>
-    <row r="681" ht="15.75" customHeight="1">
-      <c r="H681" s="2"/>
-      <c r="I681" s="2"/>
-      <c r="J681" s="3"/>
-      <c r="K681" s="4"/>
-      <c r="L681" s="2"/>
-      <c r="M681" s="5"/>
-      <c r="N681" s="6"/>
-    </row>
-    <row r="682" ht="15.75" customHeight="1">
-      <c r="H682" s="2"/>
-      <c r="I682" s="2"/>
-      <c r="J682" s="3"/>
-      <c r="K682" s="4"/>
-      <c r="L682" s="2"/>
-      <c r="M682" s="5"/>
-      <c r="N682" s="6"/>
-    </row>
-    <row r="683" ht="15.75" customHeight="1">
-      <c r="H683" s="2"/>
-      <c r="I683" s="2"/>
-      <c r="J683" s="3"/>
-      <c r="K683" s="4"/>
-      <c r="L683" s="2"/>
-      <c r="M683" s="5"/>
-      <c r="N683" s="6"/>
-    </row>
-    <row r="684" ht="15.75" customHeight="1">
-      <c r="H684" s="2"/>
-      <c r="I684" s="2"/>
-      <c r="J684" s="3"/>
-      <c r="K684" s="4"/>
-      <c r="L684" s="2"/>
-      <c r="M684" s="5"/>
-      <c r="N684" s="6"/>
-    </row>
-    <row r="685" ht="15.75" customHeight="1">
-      <c r="H685" s="2"/>
-      <c r="I685" s="2"/>
-      <c r="J685" s="3"/>
-      <c r="K685" s="4"/>
-      <c r="L685" s="2"/>
-      <c r="M685" s="5"/>
-      <c r="N685" s="6"/>
-    </row>
-    <row r="686" ht="15.75" customHeight="1">
-      <c r="H686" s="2"/>
-      <c r="I686" s="2"/>
-      <c r="J686" s="3"/>
-      <c r="K686" s="4"/>
-      <c r="L686" s="2"/>
-      <c r="M686" s="5"/>
-      <c r="N686" s="6"/>
-    </row>
-    <row r="687" ht="15.75" customHeight="1">
-      <c r="H687" s="2"/>
-      <c r="I687" s="2"/>
-      <c r="J687" s="3"/>
-      <c r="K687" s="4"/>
-      <c r="L687" s="2"/>
-      <c r="M687" s="5"/>
-      <c r="N687" s="6"/>
-    </row>
-    <row r="688" ht="15.75" customHeight="1">
-      <c r="H688" s="2"/>
-      <c r="I688" s="2"/>
-      <c r="J688" s="3"/>
-      <c r="K688" s="4"/>
-      <c r="L688" s="2"/>
-      <c r="M688" s="5"/>
-      <c r="N688" s="6"/>
-    </row>
-    <row r="689" ht="15.75" customHeight="1">
-      <c r="H689" s="2"/>
-      <c r="I689" s="2"/>
-      <c r="J689" s="3"/>
-      <c r="K689" s="4"/>
-      <c r="L689" s="2"/>
-      <c r="M689" s="5"/>
-      <c r="N689" s="6"/>
-    </row>
-    <row r="690" ht="15.75" customHeight="1">
-      <c r="H690" s="2"/>
-      <c r="I690" s="2"/>
-      <c r="J690" s="3"/>
-      <c r="K690" s="4"/>
-      <c r="L690" s="2"/>
-      <c r="M690" s="5"/>
-      <c r="N690" s="6"/>
-    </row>
-    <row r="691" ht="15.75" customHeight="1">
-      <c r="H691" s="2"/>
-      <c r="I691" s="2"/>
-      <c r="J691" s="3"/>
-      <c r="K691" s="4"/>
-      <c r="L691" s="2"/>
-      <c r="M691" s="5"/>
-      <c r="N691" s="6"/>
-    </row>
-    <row r="692" ht="15.75" customHeight="1">
-      <c r="H692" s="2"/>
-      <c r="I692" s="2"/>
-      <c r="J692" s="3"/>
-      <c r="K692" s="4"/>
-      <c r="L692" s="2"/>
-      <c r="M692" s="5"/>
-      <c r="N692" s="6"/>
-    </row>
-    <row r="693" ht="15.75" customHeight="1">
-      <c r="H693" s="2"/>
-      <c r="I693" s="2"/>
-      <c r="J693" s="3"/>
-      <c r="K693" s="4"/>
-      <c r="L693" s="2"/>
-      <c r="M693" s="5"/>
-      <c r="N693" s="6"/>
-    </row>
-    <row r="694" ht="15.75" customHeight="1">
-      <c r="H694" s="2"/>
-      <c r="I694" s="2"/>
-      <c r="J694" s="3"/>
-      <c r="K694" s="4"/>
-      <c r="L694" s="2"/>
-      <c r="M694" s="5"/>
-      <c r="N694" s="6"/>
-    </row>
-    <row r="695" ht="15.75" customHeight="1">
-      <c r="H695" s="2"/>
-      <c r="I695" s="2"/>
-      <c r="J695" s="3"/>
-      <c r="K695" s="4"/>
-      <c r="L695" s="2"/>
-      <c r="M695" s="5"/>
-      <c r="N695" s="6"/>
-    </row>
-    <row r="696" ht="15.75" customHeight="1">
-      <c r="H696" s="2"/>
-      <c r="I696" s="2"/>
-      <c r="J696" s="3"/>
-      <c r="K696" s="4"/>
-      <c r="L696" s="2"/>
-      <c r="M696" s="5"/>
-      <c r="N696" s="6"/>
-    </row>
-    <row r="697" ht="15.75" customHeight="1">
-      <c r="H697" s="2"/>
-      <c r="I697" s="2"/>
-      <c r="J697" s="3"/>
-      <c r="K697" s="4"/>
-      <c r="L697" s="2"/>
-      <c r="M697" s="5"/>
-      <c r="N697" s="6"/>
-    </row>
-    <row r="698" ht="15.75" customHeight="1">
-      <c r="H698" s="2"/>
-      <c r="I698" s="2"/>
-      <c r="J698" s="3"/>
-      <c r="K698" s="4"/>
-      <c r="L698" s="2"/>
-      <c r="M698" s="5"/>
-      <c r="N698" s="6"/>
-    </row>
-    <row r="699" ht="15.75" customHeight="1">
-      <c r="H699" s="2"/>
-      <c r="I699" s="2"/>
-      <c r="J699" s="3"/>
-      <c r="K699" s="4"/>
-      <c r="L699" s="2"/>
-      <c r="M699" s="5"/>
-      <c r="N699" s="6"/>
-    </row>
-    <row r="700" ht="15.75" customHeight="1">
-      <c r="H700" s="2"/>
-      <c r="I700" s="2"/>
-      <c r="J700" s="3"/>
-      <c r="K700" s="4"/>
-      <c r="L700" s="2"/>
-      <c r="M700" s="5"/>
-      <c r="N700" s="6"/>
-    </row>
-    <row r="701" ht="15.75" customHeight="1">
-      <c r="H701" s="2"/>
-      <c r="I701" s="2"/>
-      <c r="J701" s="3"/>
-      <c r="K701" s="4"/>
-      <c r="L701" s="2"/>
-      <c r="M701" s="5"/>
-      <c r="N701" s="6"/>
-    </row>
-    <row r="702" ht="15.75" customHeight="1">
-      <c r="H702" s="2"/>
-      <c r="I702" s="2"/>
-      <c r="J702" s="3"/>
-      <c r="K702" s="4"/>
-      <c r="L702" s="2"/>
-      <c r="M702" s="5"/>
-      <c r="N702" s="6"/>
-    </row>
-    <row r="703" ht="15.75" customHeight="1">
-      <c r="H703" s="2"/>
-      <c r="I703" s="2"/>
-      <c r="J703" s="3"/>
-      <c r="K703" s="4"/>
-      <c r="L703" s="2"/>
-      <c r="M703" s="5"/>
-      <c r="N703" s="6"/>
-    </row>
-    <row r="704" ht="15.75" customHeight="1">
-      <c r="H704" s="2"/>
-      <c r="I704" s="2"/>
-      <c r="J704" s="3"/>
-      <c r="K704" s="4"/>
-      <c r="L704" s="2"/>
-      <c r="M704" s="5"/>
-      <c r="N704" s="6"/>
-    </row>
-    <row r="705" ht="15.75" customHeight="1">
-      <c r="H705" s="2"/>
-      <c r="I705" s="2"/>
-      <c r="J705" s="3"/>
-      <c r="K705" s="4"/>
-      <c r="L705" s="2"/>
-      <c r="M705" s="5"/>
-      <c r="N705" s="6"/>
-    </row>
-    <row r="706" ht="15.75" customHeight="1">
-      <c r="H706" s="2"/>
-      <c r="I706" s="2"/>
-      <c r="J706" s="3"/>
-      <c r="K706" s="4"/>
-      <c r="L706" s="2"/>
-      <c r="M706" s="5"/>
-      <c r="N706" s="6"/>
-    </row>
-    <row r="707" ht="15.75" customHeight="1">
-      <c r="H707" s="2"/>
-      <c r="I707" s="2"/>
-      <c r="J707" s="3"/>
-      <c r="K707" s="4"/>
-      <c r="L707" s="2"/>
-      <c r="M707" s="5"/>
-      <c r="N707" s="6"/>
-    </row>
-    <row r="708" ht="15.75" customHeight="1">
-      <c r="H708" s="2"/>
-      <c r="I708" s="2"/>
-      <c r="J708" s="3"/>
-      <c r="K708" s="4"/>
-      <c r="L708" s="2"/>
-      <c r="M708" s="5"/>
-      <c r="N708" s="6"/>
-    </row>
-    <row r="709" ht="15.75" customHeight="1">
-      <c r="H709" s="2"/>
-      <c r="I709" s="2"/>
-      <c r="J709" s="3"/>
-      <c r="K709" s="4"/>
-      <c r="L709" s="2"/>
-      <c r="M709" s="5"/>
-      <c r="N709" s="6"/>
-    </row>
-    <row r="710" ht="15.75" customHeight="1">
-      <c r="H710" s="2"/>
-      <c r="I710" s="2"/>
-      <c r="J710" s="3"/>
-      <c r="K710" s="4"/>
-      <c r="L710" s="2"/>
-      <c r="M710" s="5"/>
-      <c r="N710" s="6"/>
-    </row>
-    <row r="711" ht="15.75" customHeight="1">
-      <c r="H711" s="2"/>
-      <c r="I711" s="2"/>
-      <c r="J711" s="3"/>
-      <c r="K711" s="4"/>
-      <c r="L711" s="2"/>
-      <c r="M711" s="5"/>
-      <c r="N711" s="6"/>
-    </row>
-    <row r="712" ht="15.75" customHeight="1">
-      <c r="H712" s="2"/>
-      <c r="I712" s="2"/>
-      <c r="J712" s="3"/>
-      <c r="K712" s="4"/>
-      <c r="L712" s="2"/>
-      <c r="M712" s="5"/>
-      <c r="N712" s="6"/>
-    </row>
-    <row r="713" ht="15.75" customHeight="1">
-      <c r="H713" s="2"/>
-      <c r="I713" s="2"/>
-      <c r="J713" s="3"/>
-      <c r="K713" s="4"/>
-      <c r="L713" s="2"/>
-      <c r="M713" s="5"/>
-      <c r="N713" s="6"/>
-    </row>
-    <row r="714" ht="15.75" customHeight="1">
-      <c r="H714" s="2"/>
-      <c r="I714" s="2"/>
-      <c r="J714" s="3"/>
-      <c r="K714" s="4"/>
-      <c r="L714" s="2"/>
-      <c r="M714" s="5"/>
-      <c r="N714" s="6"/>
-    </row>
-    <row r="715" ht="15.75" customHeight="1">
-      <c r="H715" s="2"/>
-      <c r="I715" s="2"/>
-      <c r="J715" s="3"/>
-      <c r="K715" s="4"/>
-      <c r="L715" s="2"/>
-      <c r="M715" s="5"/>
-      <c r="N715" s="6"/>
-    </row>
-    <row r="716" ht="15.75" customHeight="1">
-      <c r="H716" s="2"/>
-      <c r="I716" s="2"/>
-      <c r="J716" s="3"/>
-      <c r="K716" s="4"/>
-      <c r="L716" s="2"/>
-      <c r="M716" s="5"/>
-      <c r="N716" s="6"/>
-    </row>
-    <row r="717" ht="15.75" customHeight="1">
-      <c r="H717" s="2"/>
-      <c r="I717" s="2"/>
-      <c r="J717" s="3"/>
-      <c r="K717" s="4"/>
-      <c r="L717" s="2"/>
-      <c r="M717" s="5"/>
-      <c r="N717" s="6"/>
-    </row>
-    <row r="718" ht="15.75" customHeight="1">
-      <c r="H718" s="2"/>
-      <c r="I718" s="2"/>
-      <c r="J718" s="3"/>
-      <c r="K718" s="4"/>
-      <c r="L718" s="2"/>
-      <c r="M718" s="5"/>
-      <c r="N718" s="6"/>
-    </row>
-    <row r="719" ht="15.75" customHeight="1">
-      <c r="H719" s="2"/>
-      <c r="I719" s="2"/>
-      <c r="J719" s="3"/>
-      <c r="K719" s="4"/>
-      <c r="L719" s="2"/>
-      <c r="M719" s="5"/>
-      <c r="N719" s="6"/>
-    </row>
-    <row r="720" ht="15.75" customHeight="1">
-      <c r="H720" s="2"/>
-      <c r="I720" s="2"/>
-      <c r="J720" s="3"/>
-      <c r="K720" s="4"/>
-      <c r="L720" s="2"/>
-      <c r="M720" s="5"/>
-      <c r="N720" s="6"/>
-    </row>
-    <row r="721" ht="15.75" customHeight="1">
-      <c r="H721" s="2"/>
-      <c r="I721" s="2"/>
-      <c r="J721" s="3"/>
-      <c r="K721" s="4"/>
-      <c r="L721" s="2"/>
-      <c r="M721" s="5"/>
-      <c r="N721" s="6"/>
-    </row>
-    <row r="722" ht="15.75" customHeight="1">
-      <c r="H722" s="2"/>
-      <c r="I722" s="2"/>
-      <c r="J722" s="3"/>
-      <c r="K722" s="4"/>
-      <c r="L722" s="2"/>
-      <c r="M722" s="5"/>
-      <c r="N722" s="6"/>
-    </row>
-    <row r="723" ht="15.75" customHeight="1">
-      <c r="H723" s="2"/>
-      <c r="I723" s="2"/>
-      <c r="J723" s="3"/>
-      <c r="K723" s="4"/>
-      <c r="L723" s="2"/>
-      <c r="M723" s="5"/>
-      <c r="N723" s="6"/>
-    </row>
-    <row r="724" ht="15.75" customHeight="1">
-      <c r="H724" s="2"/>
-      <c r="I724" s="2"/>
-      <c r="J724" s="3"/>
-      <c r="K724" s="4"/>
-      <c r="L724" s="2"/>
-      <c r="M724" s="5"/>
-      <c r="N724" s="6"/>
-    </row>
-    <row r="725" ht="15.75" customHeight="1">
-      <c r="H725" s="2"/>
-      <c r="I725" s="2"/>
-      <c r="J725" s="3"/>
-      <c r="K725" s="4"/>
-      <c r="L725" s="2"/>
-      <c r="M725" s="5"/>
-      <c r="N725" s="6"/>
-    </row>
-    <row r="726" ht="15.75" customHeight="1">
-      <c r="H726" s="2"/>
-      <c r="I726" s="2"/>
-      <c r="J726" s="3"/>
-      <c r="K726" s="4"/>
-      <c r="L726" s="2"/>
-      <c r="M726" s="5"/>
-      <c r="N726" s="6"/>
-    </row>
-    <row r="727" ht="15.75" customHeight="1">
-      <c r="H727" s="2"/>
-      <c r="I727" s="2"/>
-      <c r="J727" s="3"/>
-      <c r="K727" s="4"/>
-      <c r="L727" s="2"/>
-      <c r="M727" s="5"/>
-      <c r="N727" s="6"/>
-    </row>
-    <row r="728" ht="15.75" customHeight="1">
-      <c r="H728" s="2"/>
-      <c r="I728" s="2"/>
-      <c r="J728" s="3"/>
-      <c r="K728" s="4"/>
-      <c r="L728" s="2"/>
-      <c r="M728" s="5"/>
-      <c r="N728" s="6"/>
-    </row>
-    <row r="729" ht="15.75" customHeight="1">
-      <c r="H729" s="2"/>
-      <c r="I729" s="2"/>
-      <c r="J729" s="3"/>
-      <c r="K729" s="4"/>
-      <c r="L729" s="2"/>
-      <c r="M729" s="5"/>
-      <c r="N729" s="6"/>
-    </row>
-    <row r="730" ht="15.75" customHeight="1">
-      <c r="H730" s="2"/>
-      <c r="I730" s="2"/>
-      <c r="J730" s="3"/>
-      <c r="K730" s="4"/>
-      <c r="L730" s="2"/>
-      <c r="M730" s="5"/>
-      <c r="N730" s="6"/>
-    </row>
-    <row r="731" ht="15.75" customHeight="1">
-      <c r="H731" s="2"/>
-      <c r="I731" s="2"/>
-      <c r="J731" s="3"/>
-      <c r="K731" s="4"/>
-      <c r="L731" s="2"/>
-      <c r="M731" s="5"/>
-      <c r="N731" s="6"/>
-    </row>
-    <row r="732" ht="15.75" customHeight="1">
-      <c r="H732" s="2"/>
-      <c r="I732" s="2"/>
-      <c r="J732" s="3"/>
-      <c r="K732" s="4"/>
-      <c r="L732" s="2"/>
-      <c r="M732" s="5"/>
-      <c r="N732" s="6"/>
-    </row>
-    <row r="733" ht="15.75" customHeight="1">
-      <c r="H733" s="2"/>
-      <c r="I733" s="2"/>
-      <c r="J733" s="3"/>
-      <c r="K733" s="4"/>
-      <c r="L733" s="2"/>
-      <c r="M733" s="5"/>
-      <c r="N733" s="6"/>
-    </row>
-    <row r="734" ht="15.75" customHeight="1">
-      <c r="H734" s="2"/>
-      <c r="I734" s="2"/>
-      <c r="J734" s="3"/>
-      <c r="K734" s="4"/>
-      <c r="L734" s="2"/>
-      <c r="M734" s="5"/>
-      <c r="N734" s="6"/>
-    </row>
-    <row r="735" ht="15.75" customHeight="1">
-      <c r="H735" s="2"/>
-      <c r="I735" s="2"/>
-      <c r="J735" s="3"/>
-      <c r="K735" s="4"/>
-      <c r="L735" s="2"/>
-      <c r="M735" s="5"/>
-      <c r="N735" s="6"/>
-    </row>
-    <row r="736" ht="15.75" customHeight="1">
-      <c r="H736" s="2"/>
-      <c r="I736" s="2"/>
-      <c r="J736" s="3"/>
-      <c r="K736" s="4"/>
-      <c r="L736" s="2"/>
-      <c r="M736" s="5"/>
-      <c r="N736" s="6"/>
-    </row>
-    <row r="737" ht="15.75" customHeight="1">
-      <c r="H737" s="2"/>
-      <c r="I737" s="2"/>
-      <c r="J737" s="3"/>
-      <c r="K737" s="4"/>
-      <c r="L737" s="2"/>
-      <c r="M737" s="5"/>
-      <c r="N737" s="6"/>
-    </row>
-    <row r="738" ht="15.75" customHeight="1">
-      <c r="H738" s="2"/>
-      <c r="I738" s="2"/>
-      <c r="J738" s="3"/>
-      <c r="K738" s="4"/>
-      <c r="L738" s="2"/>
-      <c r="M738" s="5"/>
-      <c r="N738" s="6"/>
-    </row>
-    <row r="739" ht="15.75" customHeight="1">
-      <c r="H739" s="2"/>
-      <c r="I739" s="2"/>
-      <c r="J739" s="3"/>
-      <c r="K739" s="4"/>
-      <c r="L739" s="2"/>
-      <c r="M739" s="5"/>
-      <c r="N739" s="6"/>
-    </row>
-    <row r="740" ht="15.75" customHeight="1">
-      <c r="H740" s="2"/>
-      <c r="I740" s="2"/>
-      <c r="J740" s="3"/>
-      <c r="K740" s="4"/>
-      <c r="L740" s="2"/>
-      <c r="M740" s="5"/>
-      <c r="N740" s="6"/>
-    </row>
-    <row r="741" ht="15.75" customHeight="1">
-      <c r="H741" s="2"/>
-      <c r="I741" s="2"/>
-      <c r="J741" s="3"/>
-      <c r="K741" s="4"/>
-      <c r="L741" s="2"/>
-      <c r="M741" s="5"/>
-      <c r="N741" s="6"/>
-    </row>
-    <row r="742" ht="15.75" customHeight="1">
-      <c r="H742" s="2"/>
-      <c r="I742" s="2"/>
-      <c r="J742" s="3"/>
-      <c r="K742" s="4"/>
-      <c r="L742" s="2"/>
-      <c r="M742" s="5"/>
-      <c r="N742" s="6"/>
-    </row>
-    <row r="743" ht="15.75" customHeight="1">
-      <c r="H743" s="2"/>
-      <c r="I743" s="2"/>
-      <c r="J743" s="3"/>
-      <c r="K743" s="4"/>
-      <c r="L743" s="2"/>
-      <c r="M743" s="5"/>
-      <c r="N743" s="6"/>
-    </row>
-    <row r="744" ht="15.75" customHeight="1">
-      <c r="H744" s="2"/>
-      <c r="I744" s="2"/>
-      <c r="J744" s="3"/>
-      <c r="K744" s="4"/>
-      <c r="L744" s="2"/>
-      <c r="M744" s="5"/>
-      <c r="N744" s="6"/>
-    </row>
-    <row r="745" ht="15.75" customHeight="1">
-      <c r="H745" s="2"/>
-      <c r="I745" s="2"/>
-      <c r="J745" s="3"/>
-      <c r="K745" s="4"/>
-      <c r="L745" s="2"/>
-      <c r="M745" s="5"/>
-      <c r="N745" s="6"/>
-    </row>
-    <row r="746" ht="15.75" customHeight="1">
-      <c r="H746" s="2"/>
-      <c r="I746" s="2"/>
-      <c r="J746" s="3"/>
-      <c r="K746" s="4"/>
-      <c r="L746" s="2"/>
-      <c r="M746" s="5"/>
-      <c r="N746" s="6"/>
-    </row>
-    <row r="747" ht="15.75" customHeight="1">
-      <c r="H747" s="2"/>
-      <c r="I747" s="2"/>
-      <c r="J747" s="3"/>
-      <c r="K747" s="4"/>
-      <c r="L747" s="2"/>
-      <c r="M747" s="5"/>
-      <c r="N747" s="6"/>
-    </row>
-    <row r="748" ht="15.75" customHeight="1">
-      <c r="H748" s="2"/>
-      <c r="I748" s="2"/>
-      <c r="J748" s="3"/>
-      <c r="K748" s="4"/>
-      <c r="L748" s="2"/>
-      <c r="M748" s="5"/>
-      <c r="N748" s="6"/>
-    </row>
-    <row r="749" ht="15.75" customHeight="1">
-      <c r="H749" s="2"/>
-      <c r="I749" s="2"/>
-      <c r="J749" s="3"/>
-      <c r="K749" s="4"/>
-      <c r="L749" s="2"/>
-      <c r="M749" s="5"/>
-      <c r="N749" s="6"/>
-    </row>
-    <row r="750" ht="15.75" customHeight="1">
-      <c r="H750" s="2"/>
-      <c r="I750" s="2"/>
-      <c r="J750" s="3"/>
-      <c r="K750" s="4"/>
-      <c r="L750" s="2"/>
-      <c r="M750" s="5"/>
-      <c r="N750" s="6"/>
-    </row>
-    <row r="751" ht="15.75" customHeight="1">
-      <c r="H751" s="2"/>
-      <c r="I751" s="2"/>
-      <c r="J751" s="3"/>
-      <c r="K751" s="4"/>
-      <c r="L751" s="2"/>
-      <c r="M751" s="5"/>
-      <c r="N751" s="6"/>
-    </row>
-    <row r="752" ht="15.75" customHeight="1">
-      <c r="H752" s="2"/>
-      <c r="I752" s="2"/>
-      <c r="J752" s="3"/>
-      <c r="K752" s="4"/>
-      <c r="L752" s="2"/>
-      <c r="M752" s="5"/>
-      <c r="N752" s="6"/>
-    </row>
-    <row r="753" ht="15.75" customHeight="1">
-      <c r="H753" s="2"/>
-      <c r="I753" s="2"/>
-      <c r="J753" s="3"/>
-      <c r="K753" s="4"/>
-      <c r="L753" s="2"/>
-      <c r="M753" s="5"/>
-      <c r="N753" s="6"/>
-    </row>
-    <row r="754" ht="15.75" customHeight="1">
-      <c r="H754" s="2"/>
-      <c r="I754" s="2"/>
-      <c r="J754" s="3"/>
-      <c r="K754" s="4"/>
-      <c r="L754" s="2"/>
-      <c r="M754" s="5"/>
-      <c r="N754" s="6"/>
-    </row>
-    <row r="755" ht="15.75" customHeight="1">
-      <c r="H755" s="2"/>
-      <c r="I755" s="2"/>
-      <c r="J755" s="3"/>
-      <c r="K755" s="4"/>
-      <c r="L755" s="2"/>
-      <c r="M755" s="5"/>
-      <c r="N755" s="6"/>
-    </row>
-    <row r="756" ht="15.75" customHeight="1">
-      <c r="H756" s="2"/>
-      <c r="I756" s="2"/>
-      <c r="J756" s="3"/>
-      <c r="K756" s="4"/>
-      <c r="L756" s="2"/>
-      <c r="M756" s="5"/>
-      <c r="N756" s="6"/>
-    </row>
-    <row r="757" ht="15.75" customHeight="1">
-      <c r="H757" s="2"/>
-      <c r="I757" s="2"/>
-      <c r="J757" s="3"/>
-      <c r="K757" s="4"/>
-      <c r="L757" s="2"/>
-      <c r="M757" s="5"/>
-      <c r="N757" s="6"/>
-    </row>
-    <row r="758" ht="15.75" customHeight="1">
-      <c r="H758" s="2"/>
-      <c r="I758" s="2"/>
-      <c r="J758" s="3"/>
-      <c r="K758" s="4"/>
-      <c r="L758" s="2"/>
-      <c r="M758" s="5"/>
-      <c r="N758" s="6"/>
-    </row>
-    <row r="759" ht="15.75" customHeight="1">
-      <c r="H759" s="2"/>
-      <c r="I759" s="2"/>
-      <c r="J759" s="3"/>
-      <c r="K759" s="4"/>
-      <c r="L759" s="2"/>
-      <c r="M759" s="5"/>
-      <c r="N759" s="6"/>
-    </row>
-    <row r="760" ht="15.75" customHeight="1">
-      <c r="H760" s="2"/>
-      <c r="I760" s="2"/>
-      <c r="J760" s="3"/>
-      <c r="K760" s="4"/>
-      <c r="L760" s="2"/>
-      <c r="M760" s="5"/>
-      <c r="N760" s="6"/>
-    </row>
-    <row r="761" ht="15.75" customHeight="1">
-      <c r="H761" s="2"/>
-      <c r="I761" s="2"/>
-      <c r="J761" s="3"/>
-      <c r="K761" s="4"/>
-      <c r="L761" s="2"/>
-      <c r="M761" s="5"/>
-      <c r="N761" s="6"/>
-    </row>
-    <row r="762" ht="15.75" customHeight="1">
-      <c r="H762" s="2"/>
-      <c r="I762" s="2"/>
-      <c r="J762" s="3"/>
-      <c r="K762" s="4"/>
-      <c r="L762" s="2"/>
-      <c r="M762" s="5"/>
-      <c r="N762" s="6"/>
-    </row>
-    <row r="763" ht="15.75" customHeight="1">
-      <c r="H763" s="2"/>
-      <c r="I763" s="2"/>
-      <c r="J763" s="3"/>
-      <c r="K763" s="4"/>
-      <c r="L763" s="2"/>
-      <c r="M763" s="5"/>
-      <c r="N763" s="6"/>
-    </row>
-    <row r="764" ht="15.75" customHeight="1">
-      <c r="H764" s="2"/>
-      <c r="I764" s="2"/>
-      <c r="J764" s="3"/>
-      <c r="K764" s="4"/>
-      <c r="L764" s="2"/>
-      <c r="M764" s="5"/>
-      <c r="N764" s="6"/>
-    </row>
-    <row r="765" ht="15.75" customHeight="1">
-      <c r="H765" s="2"/>
-      <c r="I765" s="2"/>
-      <c r="J765" s="3"/>
-      <c r="K765" s="4"/>
-      <c r="L765" s="2"/>
-      <c r="M765" s="5"/>
-      <c r="N765" s="6"/>
-    </row>
-    <row r="766" ht="15.75" customHeight="1">
-      <c r="H766" s="2"/>
-      <c r="I766" s="2"/>
-      <c r="J766" s="3"/>
-      <c r="K766" s="4"/>
-      <c r="L766" s="2"/>
-      <c r="M766" s="5"/>
-      <c r="N766" s="6"/>
-    </row>
-    <row r="767" ht="15.75" customHeight="1">
-      <c r="H767" s="2"/>
-      <c r="I767" s="2"/>
-      <c r="J767" s="3"/>
-      <c r="K767" s="4"/>
-      <c r="L767" s="2"/>
-      <c r="M767" s="5"/>
-      <c r="N767" s="6"/>
-    </row>
-    <row r="768" ht="15.75" customHeight="1">
-      <c r="H768" s="2"/>
-      <c r="I768" s="2"/>
-      <c r="J768" s="3"/>
-      <c r="K768" s="4"/>
-      <c r="L768" s="2"/>
-      <c r="M768" s="5"/>
-      <c r="N768" s="6"/>
-    </row>
-    <row r="769" ht="15.75" customHeight="1">
-      <c r="H769" s="2"/>
-      <c r="I769" s="2"/>
-      <c r="J769" s="3"/>
-      <c r="K769" s="4"/>
-      <c r="L769" s="2"/>
-      <c r="M769" s="5"/>
-      <c r="N769" s="6"/>
-    </row>
-    <row r="770" ht="15.75" customHeight="1">
-      <c r="H770" s="2"/>
-      <c r="I770" s="2"/>
-      <c r="J770" s="3"/>
-      <c r="K770" s="4"/>
-      <c r="L770" s="2"/>
-      <c r="M770" s="5"/>
-      <c r="N770" s="6"/>
-    </row>
-    <row r="771" ht="15.75" customHeight="1">
-      <c r="H771" s="2"/>
-      <c r="I771" s="2"/>
-      <c r="J771" s="3"/>
-      <c r="K771" s="4"/>
-      <c r="L771" s="2"/>
-      <c r="M771" s="5"/>
-      <c r="N771" s="6"/>
-    </row>
-    <row r="772" ht="15.75" customHeight="1">
-      <c r="H772" s="2"/>
-      <c r="I772" s="2"/>
-      <c r="J772" s="3"/>
-      <c r="K772" s="4"/>
-      <c r="L772" s="2"/>
-      <c r="M772" s="5"/>
-      <c r="N772" s="6"/>
-    </row>
-    <row r="773" ht="15.75" customHeight="1">
-      <c r="H773" s="2"/>
-      <c r="I773" s="2"/>
-      <c r="J773" s="3"/>
-      <c r="K773" s="4"/>
-      <c r="L773" s="2"/>
-      <c r="M773" s="5"/>
-      <c r="N773" s="6"/>
-    </row>
-    <row r="774" ht="15.75" customHeight="1">
-      <c r="H774" s="2"/>
-      <c r="I774" s="2"/>
-      <c r="J774" s="3"/>
-      <c r="K774" s="4"/>
-      <c r="L774" s="2"/>
-      <c r="M774" s="5"/>
-      <c r="N774" s="6"/>
-    </row>
-    <row r="775" ht="15.75" customHeight="1">
-      <c r="H775" s="2"/>
-      <c r="I775" s="2"/>
-      <c r="J775" s="3"/>
-      <c r="K775" s="4"/>
-      <c r="L775" s="2"/>
-      <c r="M775" s="5"/>
-      <c r="N775" s="6"/>
-    </row>
-    <row r="776" ht="15.75" customHeight="1">
-      <c r="H776" s="2"/>
-      <c r="I776" s="2"/>
-      <c r="J776" s="3"/>
-      <c r="K776" s="4"/>
-      <c r="L776" s="2"/>
-      <c r="M776" s="5"/>
-      <c r="N776" s="6"/>
-    </row>
-    <row r="777" ht="15.75" customHeight="1">
-      <c r="H777" s="2"/>
-      <c r="I777" s="2"/>
-      <c r="J777" s="3"/>
-      <c r="K777" s="4"/>
-      <c r="L777" s="2"/>
-      <c r="M777" s="5"/>
-      <c r="N777" s="6"/>
-    </row>
-    <row r="778" ht="15.75" customHeight="1">
-      <c r="H778" s="2"/>
-      <c r="I778" s="2"/>
-      <c r="J778" s="3"/>
-      <c r="K778" s="4"/>
-      <c r="L778" s="2"/>
-      <c r="M778" s="5"/>
-      <c r="N778" s="6"/>
-    </row>
-    <row r="779" ht="15.75" customHeight="1">
-      <c r="H779" s="2"/>
-      <c r="I779" s="2"/>
-      <c r="J779" s="3"/>
-      <c r="K779" s="4"/>
-      <c r="L779" s="2"/>
-      <c r="M779" s="5"/>
-      <c r="N779" s="6"/>
-    </row>
-    <row r="780" ht="15.75" customHeight="1">
-      <c r="H780" s="2"/>
-      <c r="I780" s="2"/>
-      <c r="J780" s="3"/>
-      <c r="K780" s="4"/>
-      <c r="L780" s="2"/>
-      <c r="M780" s="5"/>
-      <c r="N780" s="6"/>
-    </row>
-    <row r="781" ht="15.75" customHeight="1">
-      <c r="H781" s="2"/>
-      <c r="I781" s="2"/>
-      <c r="J781" s="3"/>
-      <c r="K781" s="4"/>
-      <c r="L781" s="2"/>
-      <c r="M781" s="5"/>
-      <c r="N781" s="6"/>
-    </row>
-    <row r="782" ht="15.75" customHeight="1">
-      <c r="H782" s="2"/>
-      <c r="I782" s="2"/>
-      <c r="J782" s="3"/>
-      <c r="K782" s="4"/>
-      <c r="L782" s="2"/>
-      <c r="M782" s="5"/>
-      <c r="N782" s="6"/>
-    </row>
-    <row r="783" ht="15.75" customHeight="1">
-      <c r="H783" s="2"/>
-      <c r="I783" s="2"/>
-      <c r="J783" s="3"/>
-      <c r="K783" s="4"/>
-      <c r="L783" s="2"/>
-      <c r="M783" s="5"/>
-      <c r="N783" s="6"/>
-    </row>
-    <row r="784" ht="15.75" customHeight="1">
-      <c r="H784" s="2"/>
-      <c r="I784" s="2"/>
-      <c r="J784" s="3"/>
-      <c r="K784" s="4"/>
-      <c r="L784" s="2"/>
-      <c r="M784" s="5"/>
-      <c r="N784" s="6"/>
-    </row>
-    <row r="785" ht="15.75" customHeight="1">
-      <c r="H785" s="2"/>
-      <c r="I785" s="2"/>
-      <c r="J785" s="3"/>
-      <c r="K785" s="4"/>
-      <c r="L785" s="2"/>
-      <c r="M785" s="5"/>
-      <c r="N785" s="6"/>
-    </row>
-    <row r="786" ht="15.75" customHeight="1">
-      <c r="H786" s="2"/>
-      <c r="I786" s="2"/>
-      <c r="J786" s="3"/>
-      <c r="K786" s="4"/>
-      <c r="L786" s="2"/>
-      <c r="M786" s="5"/>
-      <c r="N786" s="6"/>
-    </row>
-    <row r="787" ht="15.75" customHeight="1">
-      <c r="H787" s="2"/>
-      <c r="I787" s="2"/>
-      <c r="J787" s="3"/>
-      <c r="K787" s="4"/>
-      <c r="L787" s="2"/>
-      <c r="M787" s="5"/>
-      <c r="N787" s="6"/>
-    </row>
-    <row r="788" ht="15.75" customHeight="1">
-      <c r="H788" s="2"/>
-      <c r="I788" s="2"/>
-      <c r="J788" s="3"/>
-      <c r="K788" s="4"/>
-      <c r="L788" s="2"/>
-      <c r="M788" s="5"/>
-      <c r="N788" s="6"/>
-    </row>
-    <row r="789" ht="15.75" customHeight="1">
-      <c r="H789" s="2"/>
-      <c r="I789" s="2"/>
-      <c r="J789" s="3"/>
-      <c r="K789" s="4"/>
-      <c r="L789" s="2"/>
-      <c r="M789" s="5"/>
-      <c r="N789" s="6"/>
-    </row>
-    <row r="790" ht="15.75" customHeight="1">
-      <c r="H790" s="2"/>
-      <c r="I790" s="2"/>
-      <c r="J790" s="3"/>
-      <c r="K790" s="4"/>
-      <c r="L790" s="2"/>
-      <c r="M790" s="5"/>
-      <c r="N790" s="6"/>
-    </row>
-    <row r="791" ht="15.75" customHeight="1">
-      <c r="H791" s="2"/>
-      <c r="I791" s="2"/>
-      <c r="J791" s="3"/>
-      <c r="K791" s="4"/>
-      <c r="L791" s="2"/>
-      <c r="M791" s="5"/>
-      <c r="N791" s="6"/>
-    </row>
-    <row r="792" ht="15.75" customHeight="1">
-      <c r="H792" s="2"/>
-      <c r="I792" s="2"/>
-      <c r="J792" s="3"/>
-      <c r="K792" s="4"/>
-      <c r="L792" s="2"/>
-      <c r="M792" s="5"/>
-      <c r="N792" s="6"/>
-    </row>
-    <row r="793" ht="15.75" customHeight="1">
-      <c r="H793" s="2"/>
-      <c r="I793" s="2"/>
-      <c r="J793" s="3"/>
-      <c r="K793" s="4"/>
-      <c r="L793" s="2"/>
-      <c r="M793" s="5"/>
-      <c r="N793" s="6"/>
-    </row>
-    <row r="794" ht="15.75" customHeight="1">
-      <c r="H794" s="2"/>
-      <c r="I794" s="2"/>
-      <c r="J794" s="3"/>
-      <c r="K794" s="4"/>
-      <c r="L794" s="2"/>
-      <c r="M794" s="5"/>
-      <c r="N794" s="6"/>
-    </row>
-    <row r="795" ht="15.75" customHeight="1">
-      <c r="H795" s="2"/>
-      <c r="I795" s="2"/>
-      <c r="J795" s="3"/>
-      <c r="K795" s="4"/>
-      <c r="L795" s="2"/>
-      <c r="M795" s="5"/>
-      <c r="N795" s="6"/>
-    </row>
-    <row r="796" ht="15.75" customHeight="1">
-      <c r="H796" s="2"/>
-      <c r="I796" s="2"/>
-      <c r="J796" s="3"/>
-      <c r="K796" s="4"/>
-      <c r="L796" s="2"/>
-      <c r="M796" s="5"/>
-      <c r="N796" s="6"/>
-    </row>
-    <row r="797" ht="15.75" customHeight="1">
-      <c r="H797" s="2"/>
-      <c r="I797" s="2"/>
-      <c r="J797" s="3"/>
-      <c r="K797" s="4"/>
-      <c r="L797" s="2"/>
-      <c r="M797" s="5"/>
-      <c r="N797" s="6"/>
-    </row>
-    <row r="798" ht="15.75" customHeight="1">
-      <c r="H798" s="2"/>
-      <c r="I798" s="2"/>
-      <c r="J798" s="3"/>
-      <c r="K798" s="4"/>
-      <c r="L798" s="2"/>
-      <c r="M798" s="5"/>
-      <c r="N798" s="6"/>
-    </row>
-    <row r="799" ht="15.75" customHeight="1">
-      <c r="H799" s="2"/>
-      <c r="I799" s="2"/>
-      <c r="J799" s="3"/>
-      <c r="K799" s="4"/>
-      <c r="L799" s="2"/>
-      <c r="M799" s="5"/>
-      <c r="N799" s="6"/>
-    </row>
-    <row r="800" ht="15.75" customHeight="1">
-      <c r="H800" s="2"/>
-      <c r="I800" s="2"/>
-      <c r="J800" s="3"/>
-      <c r="K800" s="4"/>
-      <c r="L800" s="2"/>
-      <c r="M800" s="5"/>
-      <c r="N800" s="6"/>
-    </row>
-    <row r="801" ht="15.75" customHeight="1">
-      <c r="H801" s="2"/>
-      <c r="I801" s="2"/>
-      <c r="J801" s="3"/>
-      <c r="K801" s="4"/>
-      <c r="L801" s="2"/>
-      <c r="M801" s="5"/>
-      <c r="N801" s="6"/>
-    </row>
-    <row r="802" ht="15.75" customHeight="1">
-      <c r="H802" s="2"/>
-      <c r="I802" s="2"/>
-      <c r="J802" s="3"/>
-      <c r="K802" s="4"/>
-      <c r="L802" s="2"/>
-      <c r="M802" s="5"/>
-      <c r="N802" s="6"/>
-    </row>
-    <row r="803" ht="15.75" customHeight="1">
-      <c r="H803" s="2"/>
-      <c r="I803" s="2"/>
-      <c r="J803" s="3"/>
-      <c r="K803" s="4"/>
-      <c r="L803" s="2"/>
-      <c r="M803" s="5"/>
-      <c r="N803" s="6"/>
-    </row>
-    <row r="804" ht="15.75" customHeight="1">
-      <c r="H804" s="2"/>
-      <c r="I804" s="2"/>
-      <c r="J804" s="3"/>
-      <c r="K804" s="4"/>
-      <c r="L804" s="2"/>
-      <c r="M804" s="5"/>
-      <c r="N804" s="6"/>
-    </row>
-    <row r="805" ht="15.75" customHeight="1">
-      <c r="H805" s="2"/>
-      <c r="I805" s="2"/>
-      <c r="J805" s="3"/>
-      <c r="K805" s="4"/>
-      <c r="L805" s="2"/>
-      <c r="M805" s="5"/>
-      <c r="N805" s="6"/>
-    </row>
-    <row r="806" ht="15.75" customHeight="1">
-      <c r="H806" s="2"/>
-      <c r="I806" s="2"/>
-      <c r="J806" s="3"/>
-      <c r="K806" s="4"/>
-      <c r="L806" s="2"/>
-      <c r="M806" s="5"/>
-      <c r="N806" s="6"/>
-    </row>
-    <row r="807" ht="15.75" customHeight="1">
-      <c r="H807" s="2"/>
-      <c r="I807" s="2"/>
-      <c r="J807" s="3"/>
-      <c r="K807" s="4"/>
-      <c r="L807" s="2"/>
-      <c r="M807" s="5"/>
-      <c r="N807" s="6"/>
-    </row>
-    <row r="808" ht="15.75" customHeight="1">
-      <c r="H808" s="2"/>
-      <c r="I808" s="2"/>
-      <c r="J808" s="3"/>
-      <c r="K808" s="4"/>
-      <c r="L808" s="2"/>
-      <c r="M808" s="5"/>
-      <c r="N808" s="6"/>
-    </row>
-    <row r="809" ht="15.75" customHeight="1">
-      <c r="H809" s="2"/>
-      <c r="I809" s="2"/>
-      <c r="J809" s="3"/>
-      <c r="K809" s="4"/>
-      <c r="L809" s="2"/>
-      <c r="M809" s="5"/>
-      <c r="N809" s="6"/>
-    </row>
-    <row r="810" ht="15.75" customHeight="1">
-      <c r="H810" s="2"/>
-      <c r="I810" s="2"/>
-      <c r="J810" s="3"/>
-      <c r="K810" s="4"/>
-      <c r="L810" s="2"/>
-      <c r="M810" s="5"/>
-      <c r="N810" s="6"/>
-    </row>
-    <row r="811" ht="15.75" customHeight="1">
-      <c r="H811" s="2"/>
-      <c r="I811" s="2"/>
-      <c r="J811" s="3"/>
-      <c r="K811" s="4"/>
-      <c r="L811" s="2"/>
-      <c r="M811" s="5"/>
-      <c r="N811" s="6"/>
-    </row>
-    <row r="812" ht="15.75" customHeight="1">
-      <c r="H812" s="2"/>
-      <c r="I812" s="2"/>
-      <c r="J812" s="3"/>
-      <c r="K812" s="4"/>
-      <c r="L812" s="2"/>
-      <c r="M812" s="5"/>
-      <c r="N812" s="6"/>
-    </row>
-    <row r="813" ht="15.75" customHeight="1">
-      <c r="H813" s="2"/>
-      <c r="I813" s="2"/>
-      <c r="J813" s="3"/>
-      <c r="K813" s="4"/>
-      <c r="L813" s="2"/>
-      <c r="M813" s="5"/>
-      <c r="N813" s="6"/>
-    </row>
-    <row r="814" ht="15.75" customHeight="1">
-      <c r="H814" s="2"/>
-      <c r="I814" s="2"/>
-      <c r="J814" s="3"/>
-      <c r="K814" s="4"/>
-      <c r="L814" s="2"/>
-      <c r="M814" s="5"/>
-      <c r="N814" s="6"/>
-    </row>
-    <row r="815" ht="15.75" customHeight="1">
-      <c r="H815" s="2"/>
-      <c r="I815" s="2"/>
-      <c r="J815" s="3"/>
-      <c r="K815" s="4"/>
-      <c r="L815" s="2"/>
-      <c r="M815" s="5"/>
-      <c r="N815" s="6"/>
-    </row>
-    <row r="816" ht="15.75" customHeight="1">
-      <c r="H816" s="2"/>
-      <c r="I816" s="2"/>
-      <c r="J816" s="3"/>
-      <c r="K816" s="4"/>
-      <c r="L816" s="2"/>
-      <c r="M816" s="5"/>
-      <c r="N816" s="6"/>
-    </row>
-    <row r="817" ht="15.75" customHeight="1">
-      <c r="H817" s="2"/>
-      <c r="I817" s="2"/>
-      <c r="J817" s="3"/>
-      <c r="K817" s="4"/>
-      <c r="L817" s="2"/>
-      <c r="M817" s="5"/>
-      <c r="N817" s="6"/>
-    </row>
-    <row r="818" ht="15.75" customHeight="1">
-      <c r="H818" s="2"/>
-      <c r="I818" s="2"/>
-      <c r="J818" s="3"/>
-      <c r="K818" s="4"/>
-      <c r="L818" s="2"/>
-      <c r="M818" s="5"/>
-      <c r="N818" s="6"/>
-    </row>
-    <row r="819" ht="15.75" customHeight="1">
-      <c r="H819" s="2"/>
-      <c r="I819" s="2"/>
-      <c r="J819" s="3"/>
-      <c r="K819" s="4"/>
-      <c r="L819" s="2"/>
-      <c r="M819" s="5"/>
-      <c r="N819" s="6"/>
-    </row>
-    <row r="820" ht="15.75" customHeight="1">
-      <c r="H820" s="2"/>
-      <c r="I820" s="2"/>
-      <c r="J820" s="3"/>
-      <c r="K820" s="4"/>
-      <c r="L820" s="2"/>
-      <c r="M820" s="5"/>
-      <c r="N820" s="6"/>
-    </row>
-    <row r="821" ht="15.75" customHeight="1">
-      <c r="H821" s="2"/>
-      <c r="I821" s="2"/>
-      <c r="J821" s="3"/>
-      <c r="K821" s="4"/>
-      <c r="L821" s="2"/>
-      <c r="M821" s="5"/>
-      <c r="N821" s="6"/>
-    </row>
-    <row r="822" ht="15.75" customHeight="1">
-      <c r="H822" s="2"/>
-      <c r="I822" s="2"/>
-      <c r="J822" s="3"/>
-      <c r="K822" s="4"/>
-      <c r="L822" s="2"/>
-      <c r="M822" s="5"/>
-      <c r="N822" s="6"/>
-    </row>
-    <row r="823" ht="15.75" customHeight="1">
-      <c r="H823" s="2"/>
-      <c r="I823" s="2"/>
-      <c r="J823" s="3"/>
-      <c r="K823" s="4"/>
-      <c r="L823" s="2"/>
-      <c r="M823" s="5"/>
-      <c r="N823" s="6"/>
-    </row>
-    <row r="824" ht="15.75" customHeight="1">
-      <c r="H824" s="2"/>
-      <c r="I824" s="2"/>
-      <c r="J824" s="3"/>
-      <c r="K824" s="4"/>
-      <c r="L824" s="2"/>
-      <c r="M824" s="5"/>
-      <c r="N824" s="6"/>
-    </row>
-    <row r="825" ht="15.75" customHeight="1">
-      <c r="H825" s="2"/>
-      <c r="I825" s="2"/>
-      <c r="J825" s="3"/>
-      <c r="K825" s="4"/>
-      <c r="L825" s="2"/>
-      <c r="M825" s="5"/>
-      <c r="N825" s="6"/>
-    </row>
-    <row r="826" ht="15.75" customHeight="1">
-      <c r="H826" s="2"/>
-      <c r="I826" s="2"/>
-      <c r="J826" s="3"/>
-      <c r="K826" s="4"/>
-      <c r="L826" s="2"/>
-      <c r="M826" s="5"/>
-      <c r="N826" s="6"/>
-    </row>
-    <row r="827" ht="15.75" customHeight="1">
-      <c r="H827" s="2"/>
-      <c r="I827" s="2"/>
-      <c r="J827" s="3"/>
-      <c r="K827" s="4"/>
-      <c r="L827" s="2"/>
-      <c r="M827" s="5"/>
-      <c r="N827" s="6"/>
-    </row>
-    <row r="828" ht="15.75" customHeight="1">
-      <c r="H828" s="2"/>
-      <c r="I828" s="2"/>
-      <c r="J828" s="3"/>
-      <c r="K828" s="4"/>
-      <c r="L828" s="2"/>
-      <c r="M828" s="5"/>
-      <c r="N828" s="6"/>
-    </row>
-    <row r="829" ht="15.75" customHeight="1">
-      <c r="H829" s="2"/>
-      <c r="I829" s="2"/>
-      <c r="J829" s="3"/>
-      <c r="K829" s="4"/>
-      <c r="L829" s="2"/>
-      <c r="M829" s="5"/>
-      <c r="N829" s="6"/>
-    </row>
-    <row r="830" ht="15.75" customHeight="1">
-      <c r="H830" s="2"/>
-      <c r="I830" s="2"/>
-      <c r="J830" s="3"/>
-      <c r="K830" s="4"/>
-      <c r="L830" s="2"/>
-      <c r="M830" s="5"/>
-      <c r="N830" s="6"/>
-    </row>
-    <row r="831" ht="15.75" customHeight="1">
-      <c r="H831" s="2"/>
-      <c r="I831" s="2"/>
-      <c r="J831" s="3"/>
-      <c r="K831" s="4"/>
-      <c r="L831" s="2"/>
-      <c r="M831" s="5"/>
-      <c r="N831" s="6"/>
-    </row>
-    <row r="832" ht="15.75" customHeight="1">
-      <c r="H832" s="2"/>
-      <c r="I832" s="2"/>
-      <c r="J832" s="3"/>
-      <c r="K832" s="4"/>
-      <c r="L832" s="2"/>
-      <c r="M832" s="5"/>
-      <c r="N832" s="6"/>
-    </row>
-    <row r="833" ht="15.75" customHeight="1">
-      <c r="H833" s="2"/>
-      <c r="I833" s="2"/>
-      <c r="J833" s="3"/>
-      <c r="K833" s="4"/>
-      <c r="L833" s="2"/>
-      <c r="M833" s="5"/>
-      <c r="N833" s="6"/>
-    </row>
-    <row r="834" ht="15.75" customHeight="1">
-      <c r="H834" s="2"/>
-      <c r="I834" s="2"/>
-      <c r="J834" s="3"/>
-      <c r="K834" s="4"/>
-      <c r="L834" s="2"/>
-      <c r="M834" s="5"/>
-      <c r="N834" s="6"/>
-    </row>
-    <row r="835" ht="15.75" customHeight="1">
-      <c r="H835" s="2"/>
-      <c r="I835" s="2"/>
-      <c r="J835" s="3"/>
-      <c r="K835" s="4"/>
-      <c r="L835" s="2"/>
-      <c r="M835" s="5"/>
-      <c r="N835" s="6"/>
-    </row>
-    <row r="836" ht="15.75" customHeight="1">
-      <c r="H836" s="2"/>
-      <c r="I836" s="2"/>
-      <c r="J836" s="3"/>
-      <c r="K836" s="4"/>
-      <c r="L836" s="2"/>
-      <c r="M836" s="5"/>
-      <c r="N836" s="6"/>
-    </row>
-    <row r="837" ht="15.75" customHeight="1">
-      <c r="H837" s="2"/>
-      <c r="I837" s="2"/>
-      <c r="J837" s="3"/>
-      <c r="K837" s="4"/>
-      <c r="L837" s="2"/>
-      <c r="M837" s="5"/>
-      <c r="N837" s="6"/>
-    </row>
-    <row r="838" ht="15.75" customHeight="1">
-      <c r="H838" s="2"/>
-      <c r="I838" s="2"/>
-      <c r="J838" s="3"/>
-      <c r="K838" s="4"/>
-      <c r="L838" s="2"/>
-      <c r="M838" s="5"/>
-      <c r="N838" s="6"/>
-    </row>
-    <row r="839" ht="15.75" customHeight="1">
-      <c r="H839" s="2"/>
-      <c r="I839" s="2"/>
-      <c r="J839" s="3"/>
-      <c r="K839" s="4"/>
-      <c r="L839" s="2"/>
-      <c r="M839" s="5"/>
-      <c r="N839" s="6"/>
-    </row>
-    <row r="840" ht="15.75" customHeight="1">
-      <c r="H840" s="2"/>
-      <c r="I840" s="2"/>
-      <c r="J840" s="3"/>
-      <c r="K840" s="4"/>
-      <c r="L840" s="2"/>
-      <c r="M840" s="5"/>
-      <c r="N840" s="6"/>
-    </row>
-    <row r="841" ht="15.75" customHeight="1">
-      <c r="H841" s="2"/>
-      <c r="I841" s="2"/>
-      <c r="J841" s="3"/>
-      <c r="K841" s="4"/>
-      <c r="L841" s="2"/>
-      <c r="M841" s="5"/>
-      <c r="N841" s="6"/>
-    </row>
-    <row r="842" ht="15.75" customHeight="1">
-      <c r="H842" s="2"/>
-      <c r="I842" s="2"/>
-      <c r="J842" s="3"/>
-      <c r="K842" s="4"/>
-      <c r="L842" s="2"/>
-      <c r="M842" s="5"/>
-      <c r="N842" s="6"/>
-    </row>
-    <row r="843" ht="15.75" customHeight="1">
-      <c r="H843" s="2"/>
-      <c r="I843" s="2"/>
-      <c r="J843" s="3"/>
-      <c r="K843" s="4"/>
-      <c r="L843" s="2"/>
-      <c r="M843" s="5"/>
-      <c r="N843" s="6"/>
-    </row>
-    <row r="844" ht="15.75" customHeight="1">
-      <c r="H844" s="2"/>
-      <c r="I844" s="2"/>
-      <c r="J844" s="3"/>
-      <c r="K844" s="4"/>
-      <c r="L844" s="2"/>
-      <c r="M844" s="5"/>
-      <c r="N844" s="6"/>
-    </row>
-    <row r="845" ht="15.75" customHeight="1">
-      <c r="H845" s="2"/>
-      <c r="I845" s="2"/>
-      <c r="J845" s="3"/>
-      <c r="K845" s="4"/>
-      <c r="L845" s="2"/>
-      <c r="M845" s="5"/>
-      <c r="N845" s="6"/>
-    </row>
-    <row r="846" ht="15.75" customHeight="1">
-      <c r="H846" s="2"/>
-      <c r="I846" s="2"/>
-      <c r="J846" s="3"/>
-      <c r="K846" s="4"/>
-      <c r="L846" s="2"/>
-      <c r="M846" s="5"/>
-      <c r="N846" s="6"/>
-    </row>
-    <row r="847" ht="15.75" customHeight="1">
-      <c r="H847" s="2"/>
-      <c r="I847" s="2"/>
-      <c r="J847" s="3"/>
-      <c r="K847" s="4"/>
-      <c r="L847" s="2"/>
-      <c r="M847" s="5"/>
-      <c r="N847" s="6"/>
-    </row>
-    <row r="848" ht="15.75" customHeight="1">
-      <c r="H848" s="2"/>
-      <c r="I848" s="2"/>
-      <c r="J848" s="3"/>
-      <c r="K848" s="4"/>
-      <c r="L848" s="2"/>
-      <c r="M848" s="5"/>
-      <c r="N848" s="6"/>
-    </row>
-    <row r="849" ht="15.75" customHeight="1">
-      <c r="H849" s="2"/>
-      <c r="I849" s="2"/>
-      <c r="J849" s="3"/>
-      <c r="K849" s="4"/>
-      <c r="L849" s="2"/>
-      <c r="M849" s="5"/>
-      <c r="N849" s="6"/>
-    </row>
-    <row r="850" ht="15.75" customHeight="1">
-      <c r="H850" s="2"/>
-      <c r="I850" s="2"/>
-      <c r="J850" s="3"/>
-      <c r="K850" s="4"/>
-      <c r="L850" s="2"/>
-      <c r="M850" s="5"/>
-      <c r="N850" s="6"/>
-    </row>
-    <row r="851" ht="15.75" customHeight="1">
-      <c r="H851" s="2"/>
-      <c r="I851" s="2"/>
-      <c r="J851" s="3"/>
-      <c r="K851" s="4"/>
-      <c r="L851" s="2"/>
-      <c r="M851" s="5"/>
-      <c r="N851" s="6"/>
-    </row>
-    <row r="852" ht="15.75" customHeight="1">
-      <c r="H852" s="2"/>
-      <c r="I852" s="2"/>
-      <c r="J852" s="3"/>
-      <c r="K852" s="4"/>
-      <c r="L852" s="2"/>
-      <c r="M852" s="5"/>
-      <c r="N852" s="6"/>
-    </row>
-    <row r="853" ht="15.75" customHeight="1">
-      <c r="H853" s="2"/>
-      <c r="I853" s="2"/>
-      <c r="J853" s="3"/>
-      <c r="K853" s="4"/>
-      <c r="L853" s="2"/>
-      <c r="M853" s="5"/>
-      <c r="N853" s="6"/>
-    </row>
-    <row r="854" ht="15.75" customHeight="1">
-      <c r="H854" s="2"/>
-      <c r="I854" s="2"/>
-      <c r="J854" s="3"/>
-      <c r="K854" s="4"/>
-      <c r="L854" s="2"/>
-      <c r="M854" s="5"/>
-      <c r="N854" s="6"/>
-    </row>
-    <row r="855" ht="15.75" customHeight="1">
-      <c r="H855" s="2"/>
-      <c r="I855" s="2"/>
-      <c r="J855" s="3"/>
-      <c r="K855" s="4"/>
-      <c r="L855" s="2"/>
-      <c r="M855" s="5"/>
-      <c r="N855" s="6"/>
-    </row>
-    <row r="856" ht="15.75" customHeight="1">
-      <c r="H856" s="2"/>
-      <c r="I856" s="2"/>
-      <c r="J856" s="3"/>
-      <c r="K856" s="4"/>
-      <c r="L856" s="2"/>
-      <c r="M856" s="5"/>
-      <c r="N856" s="6"/>
-    </row>
-    <row r="857" ht="15.75" customHeight="1">
-      <c r="H857" s="2"/>
-      <c r="I857" s="2"/>
-      <c r="J857" s="3"/>
-      <c r="K857" s="4"/>
-      <c r="L857" s="2"/>
-      <c r="M857" s="5"/>
-      <c r="N857" s="6"/>
-    </row>
-    <row r="858" ht="15.75" customHeight="1">
-      <c r="H858" s="2"/>
-      <c r="I858" s="2"/>
-      <c r="J858" s="3"/>
-      <c r="K858" s="4"/>
-      <c r="L858" s="2"/>
-      <c r="M858" s="5"/>
-      <c r="N858" s="6"/>
-    </row>
-    <row r="859" ht="15.75" customHeight="1">
-      <c r="H859" s="2"/>
-      <c r="I859" s="2"/>
-      <c r="J859" s="3"/>
-      <c r="K859" s="4"/>
-      <c r="L859" s="2"/>
-      <c r="M859" s="5"/>
-      <c r="N859" s="6"/>
-    </row>
-    <row r="860" ht="15.75" customHeight="1">
-      <c r="H860" s="2"/>
-      <c r="I860" s="2"/>
-      <c r="J860" s="3"/>
-      <c r="K860" s="4"/>
-      <c r="L860" s="2"/>
-      <c r="M860" s="5"/>
-      <c r="N860" s="6"/>
-    </row>
-    <row r="861" ht="15.75" customHeight="1">
-      <c r="H861" s="2"/>
-      <c r="I861" s="2"/>
-      <c r="J861" s="3"/>
-      <c r="K861" s="4"/>
-      <c r="L861" s="2"/>
-      <c r="M861" s="5"/>
-      <c r="N861" s="6"/>
-    </row>
-    <row r="862" ht="15.75" customHeight="1">
-      <c r="H862" s="2"/>
-      <c r="I862" s="2"/>
-      <c r="J862" s="3"/>
-      <c r="K862" s="4"/>
-      <c r="L862" s="2"/>
-      <c r="M862" s="5"/>
-      <c r="N862" s="6"/>
-    </row>
-    <row r="863" ht="15.75" customHeight="1">
-      <c r="H863" s="2"/>
-      <c r="I863" s="2"/>
-      <c r="J863" s="3"/>
-      <c r="K863" s="4"/>
-      <c r="L863" s="2"/>
-      <c r="M863" s="5"/>
-      <c r="N863" s="6"/>
-    </row>
-    <row r="864" ht="15.75" customHeight="1">
-      <c r="H864" s="2"/>
-      <c r="I864" s="2"/>
-      <c r="J864" s="3"/>
-      <c r="K864" s="4"/>
-      <c r="L864" s="2"/>
-      <c r="M864" s="5"/>
-      <c r="N864" s="6"/>
-    </row>
-    <row r="865" ht="15.75" customHeight="1">
-      <c r="H865" s="2"/>
-      <c r="I865" s="2"/>
-      <c r="J865" s="3"/>
-      <c r="K865" s="4"/>
-      <c r="L865" s="2"/>
-      <c r="M865" s="5"/>
-      <c r="N865" s="6"/>
-    </row>
-    <row r="866" ht="15.75" customHeight="1">
-      <c r="H866" s="2"/>
-      <c r="I866" s="2"/>
-      <c r="J866" s="3"/>
-      <c r="K866" s="4"/>
-      <c r="L866" s="2"/>
-      <c r="M866" s="5"/>
-      <c r="N866" s="6"/>
-    </row>
-    <row r="867" ht="15.75" customHeight="1">
-      <c r="H867" s="2"/>
-      <c r="I867" s="2"/>
-      <c r="J867" s="3"/>
-      <c r="K867" s="4"/>
-      <c r="L867" s="2"/>
-      <c r="M867" s="5"/>
-      <c r="N867" s="6"/>
-    </row>
-    <row r="868" ht="15.75" customHeight="1">
-      <c r="H868" s="2"/>
-      <c r="I868" s="2"/>
-      <c r="J868" s="3"/>
-      <c r="K868" s="4"/>
-      <c r="L868" s="2"/>
-      <c r="M868" s="5"/>
-      <c r="N868" s="6"/>
-    </row>
-    <row r="869" ht="15.75" customHeight="1">
-      <c r="H869" s="2"/>
-      <c r="I869" s="2"/>
-      <c r="J869" s="3"/>
-      <c r="K869" s="4"/>
-      <c r="L869" s="2"/>
-      <c r="M869" s="5"/>
-      <c r="N869" s="6"/>
-    </row>
-    <row r="870" ht="15.75" customHeight="1">
-      <c r="H870" s="2"/>
-      <c r="I870" s="2"/>
-      <c r="J870" s="3"/>
-      <c r="K870" s="4"/>
-      <c r="L870" s="2"/>
-      <c r="M870" s="5"/>
-      <c r="N870" s="6"/>
-    </row>
-    <row r="871" ht="15.75" customHeight="1">
-      <c r="H871" s="2"/>
-      <c r="I871" s="2"/>
-      <c r="J871" s="3"/>
-      <c r="K871" s="4"/>
-      <c r="L871" s="2"/>
-      <c r="M871" s="5"/>
-      <c r="N871" s="6"/>
-    </row>
-    <row r="872" ht="15.75" customHeight="1">
-      <c r="H872" s="2"/>
-      <c r="I872" s="2"/>
-      <c r="J872" s="3"/>
-      <c r="K872" s="4"/>
-      <c r="L872" s="2"/>
-      <c r="M872" s="5"/>
-      <c r="N872" s="6"/>
-    </row>
-    <row r="873" ht="15.75" customHeight="1">
-      <c r="H873" s="2"/>
-      <c r="I873" s="2"/>
-      <c r="J873" s="3"/>
-      <c r="K873" s="4"/>
-      <c r="L873" s="2"/>
-      <c r="M873" s="5"/>
-      <c r="N873" s="6"/>
-    </row>
-    <row r="874" ht="15.75" customHeight="1">
-      <c r="H874" s="2"/>
-      <c r="I874" s="2"/>
-      <c r="J874" s="3"/>
-      <c r="K874" s="4"/>
-      <c r="L874" s="2"/>
-      <c r="M874" s="5"/>
-      <c r="N874" s="6"/>
-    </row>
-    <row r="875" ht="15.75" customHeight="1">
-      <c r="H875" s="2"/>
-      <c r="I875" s="2"/>
-      <c r="J875" s="3"/>
-      <c r="K875" s="4"/>
-      <c r="L875" s="2"/>
-      <c r="M875" s="5"/>
-      <c r="N875" s="6"/>
-    </row>
-    <row r="876" ht="15.75" customHeight="1">
-      <c r="H876" s="2"/>
-      <c r="I876" s="2"/>
-      <c r="J876" s="3"/>
-      <c r="K876" s="4"/>
-      <c r="L876" s="2"/>
-      <c r="M876" s="5"/>
-      <c r="N876" s="6"/>
-    </row>
-    <row r="877" ht="15.75" customHeight="1">
-      <c r="H877" s="2"/>
-      <c r="I877" s="2"/>
-      <c r="J877" s="3"/>
-      <c r="K877" s="4"/>
-      <c r="L877" s="2"/>
-      <c r="M877" s="5"/>
-      <c r="N877" s="6"/>
-    </row>
-    <row r="878" ht="15.75" customHeight="1">
-      <c r="H878" s="2"/>
-      <c r="I878" s="2"/>
-      <c r="J878" s="3"/>
-      <c r="K878" s="4"/>
-      <c r="L878" s="2"/>
-      <c r="M878" s="5"/>
-      <c r="N878" s="6"/>
-    </row>
-    <row r="879" ht="15.75" customHeight="1">
-      <c r="H879" s="2"/>
-      <c r="I879" s="2"/>
-      <c r="J879" s="3"/>
-      <c r="K879" s="4"/>
-      <c r="L879" s="2"/>
-      <c r="M879" s="5"/>
-      <c r="N879" s="6"/>
-    </row>
-    <row r="880" ht="15.75" customHeight="1">
-      <c r="H880" s="2"/>
-      <c r="I880" s="2"/>
-      <c r="J880" s="3"/>
-      <c r="K880" s="4"/>
-      <c r="L880" s="2"/>
-      <c r="M880" s="5"/>
-      <c r="N880" s="6"/>
-    </row>
-    <row r="881" ht="15.75" customHeight="1">
-      <c r="H881" s="2"/>
-      <c r="I881" s="2"/>
-      <c r="J881" s="3"/>
-      <c r="K881" s="4"/>
-      <c r="L881" s="2"/>
-      <c r="M881" s="5"/>
-      <c r="N881" s="6"/>
-    </row>
-    <row r="882" ht="15.75" customHeight="1">
-      <c r="H882" s="2"/>
-      <c r="I882" s="2"/>
-      <c r="J882" s="3"/>
-      <c r="K882" s="4"/>
-      <c r="L882" s="2"/>
-      <c r="M882" s="5"/>
-      <c r="N882" s="6"/>
-    </row>
-    <row r="883" ht="15.75" customHeight="1">
-      <c r="H883" s="2"/>
-      <c r="I883" s="2"/>
-      <c r="J883" s="3"/>
-      <c r="K883" s="4"/>
-      <c r="L883" s="2"/>
-      <c r="M883" s="5"/>
-      <c r="N883" s="6"/>
-    </row>
-    <row r="884" ht="15.75" customHeight="1">
-      <c r="H884" s="2"/>
-      <c r="I884" s="2"/>
-      <c r="J884" s="3"/>
-      <c r="K884" s="4"/>
-      <c r="L884" s="2"/>
-      <c r="M884" s="5"/>
-      <c r="N884" s="6"/>
-    </row>
-    <row r="885" ht="15.75" customHeight="1">
-      <c r="H885" s="2"/>
-      <c r="I885" s="2"/>
-      <c r="J885" s="3"/>
-      <c r="K885" s="4"/>
-      <c r="L885" s="2"/>
-      <c r="M885" s="5"/>
-      <c r="N885" s="6"/>
-    </row>
-    <row r="886" ht="15.75" customHeight="1">
-      <c r="H886" s="2"/>
-      <c r="I886" s="2"/>
-      <c r="J886" s="3"/>
-      <c r="K886" s="4"/>
-      <c r="L886" s="2"/>
-      <c r="M886" s="5"/>
-      <c r="N886" s="6"/>
-    </row>
-    <row r="887" ht="15.75" customHeight="1">
-      <c r="H887" s="2"/>
-      <c r="I887" s="2"/>
-      <c r="J887" s="3"/>
-      <c r="K887" s="4"/>
-      <c r="L887" s="2"/>
-      <c r="M887" s="5"/>
-      <c r="N887" s="6"/>
-    </row>
-    <row r="888" ht="15.75" customHeight="1">
-      <c r="H888" s="2"/>
-      <c r="I888" s="2"/>
-      <c r="J888" s="3"/>
-      <c r="K888" s="4"/>
-      <c r="L888" s="2"/>
-      <c r="M888" s="5"/>
-      <c r="N888" s="6"/>
-    </row>
-    <row r="889" ht="15.75" customHeight="1">
-      <c r="H889" s="2"/>
-      <c r="I889" s="2"/>
-      <c r="J889" s="3"/>
-      <c r="K889" s="4"/>
-      <c r="L889" s="2"/>
-      <c r="M889" s="5"/>
-      <c r="N889" s="6"/>
-    </row>
-    <row r="890" ht="15.75" customHeight="1">
-      <c r="H890" s="2"/>
-      <c r="I890" s="2"/>
-      <c r="J890" s="3"/>
-      <c r="K890" s="4"/>
-      <c r="L890" s="2"/>
-      <c r="M890" s="5"/>
-      <c r="N890" s="6"/>
-    </row>
-    <row r="891" ht="15.75" customHeight="1">
-      <c r="H891" s="2"/>
-      <c r="I891" s="2"/>
-      <c r="J891" s="3"/>
-      <c r="K891" s="4"/>
-      <c r="L891" s="2"/>
-      <c r="M891" s="5"/>
-      <c r="N891" s="6"/>
-    </row>
-    <row r="892" ht="15.75" customHeight="1">
-      <c r="H892" s="2"/>
-      <c r="I892" s="2"/>
-      <c r="J892" s="3"/>
-      <c r="K892" s="4"/>
-      <c r="L892" s="2"/>
-      <c r="M892" s="5"/>
-      <c r="N892" s="6"/>
-    </row>
-    <row r="893" ht="15.75" customHeight="1">
-      <c r="H893" s="2"/>
-      <c r="I893" s="2"/>
-      <c r="J893" s="3"/>
-      <c r="K893" s="4"/>
-      <c r="L893" s="2"/>
-      <c r="M893" s="5"/>
-      <c r="N893" s="6"/>
-    </row>
-    <row r="894" ht="15.75" customHeight="1">
-      <c r="H894" s="2"/>
-      <c r="I894" s="2"/>
-      <c r="J894" s="3"/>
-      <c r="K894" s="4"/>
-      <c r="L894" s="2"/>
-      <c r="M894" s="5"/>
-      <c r="N894" s="6"/>
-    </row>
-    <row r="895" ht="15.75" customHeight="1">
-      <c r="H895" s="2"/>
-      <c r="I895" s="2"/>
-      <c r="J895" s="3"/>
-      <c r="K895" s="4"/>
-      <c r="L895" s="2"/>
-      <c r="M895" s="5"/>
-      <c r="N895" s="6"/>
-    </row>
-    <row r="896" ht="15.75" customHeight="1">
-      <c r="H896" s="2"/>
-      <c r="I896" s="2"/>
-      <c r="J896" s="3"/>
-      <c r="K896" s="4"/>
-      <c r="L896" s="2"/>
-      <c r="M896" s="5"/>
-      <c r="N896" s="6"/>
-    </row>
-    <row r="897" ht="15.75" customHeight="1">
-      <c r="H897" s="2"/>
-      <c r="I897" s="2"/>
-      <c r="J897" s="3"/>
-      <c r="K897" s="4"/>
-      <c r="L897" s="2"/>
-      <c r="M897" s="5"/>
-      <c r="N897" s="6"/>
-    </row>
-    <row r="898" ht="15.75" customHeight="1">
-      <c r="H898" s="2"/>
-      <c r="I898" s="2"/>
-      <c r="J898" s="3"/>
-      <c r="K898" s="4"/>
-      <c r="L898" s="2"/>
-      <c r="M898" s="5"/>
-      <c r="N898" s="6"/>
-    </row>
-    <row r="899" ht="15.75" customHeight="1">
-      <c r="H899" s="2"/>
-      <c r="I899" s="2"/>
-      <c r="J899" s="3"/>
-      <c r="K899" s="4"/>
-      <c r="L899" s="2"/>
-      <c r="M899" s="5"/>
-      <c r="N899" s="6"/>
-    </row>
-    <row r="900" ht="15.75" customHeight="1">
-      <c r="H900" s="2"/>
-      <c r="I900" s="2"/>
-      <c r="J900" s="3"/>
-      <c r="K900" s="4"/>
-      <c r="L900" s="2"/>
-      <c r="M900" s="5"/>
-      <c r="N900" s="6"/>
-    </row>
-    <row r="901" ht="15.75" customHeight="1">
-      <c r="H901" s="2"/>
-      <c r="I901" s="2"/>
-      <c r="J901" s="3"/>
-      <c r="K901" s="4"/>
-      <c r="L901" s="2"/>
-      <c r="M901" s="5"/>
-      <c r="N901" s="6"/>
-    </row>
-    <row r="902" ht="15.75" customHeight="1">
-      <c r="H902" s="2"/>
-      <c r="I902" s="2"/>
-      <c r="J902" s="3"/>
-      <c r="K902" s="4"/>
-      <c r="L902" s="2"/>
-      <c r="M902" s="5"/>
-      <c r="N902" s="6"/>
-    </row>
-    <row r="903" ht="15.75" customHeight="1">
-      <c r="H903" s="2"/>
-      <c r="I903" s="2"/>
-      <c r="J903" s="3"/>
-      <c r="K903" s="4"/>
-      <c r="L903" s="2"/>
-      <c r="M903" s="5"/>
-      <c r="N903" s="6"/>
-    </row>
-    <row r="904" ht="15.75" customHeight="1">
-      <c r="H904" s="2"/>
-      <c r="I904" s="2"/>
-      <c r="J904" s="3"/>
-      <c r="K904" s="4"/>
-      <c r="L904" s="2"/>
-      <c r="M904" s="5"/>
-      <c r="N904" s="6"/>
-    </row>
-    <row r="905" ht="15.75" customHeight="1">
-      <c r="H905" s="2"/>
-      <c r="I905" s="2"/>
-      <c r="J905" s="3"/>
-      <c r="K905" s="4"/>
-      <c r="L905" s="2"/>
-      <c r="M905" s="5"/>
-      <c r="N905" s="6"/>
-    </row>
-    <row r="906" ht="15.75" customHeight="1">
-      <c r="H906" s="2"/>
-      <c r="I906" s="2"/>
-      <c r="J906" s="3"/>
-      <c r="K906" s="4"/>
-      <c r="L906" s="2"/>
-      <c r="M906" s="5"/>
-      <c r="N906" s="6"/>
-    </row>
-    <row r="907" ht="15.75" customHeight="1">
-      <c r="H907" s="2"/>
-      <c r="I907" s="2"/>
-      <c r="J907" s="3"/>
-      <c r="K907" s="4"/>
-      <c r="L907" s="2"/>
-      <c r="M907" s="5"/>
-      <c r="N907" s="6"/>
-    </row>
-    <row r="908" ht="15.75" customHeight="1">
-      <c r="H908" s="2"/>
-      <c r="I908" s="2"/>
-      <c r="J908" s="3"/>
-      <c r="K908" s="4"/>
-      <c r="L908" s="2"/>
-      <c r="M908" s="5"/>
-      <c r="N908" s="6"/>
-    </row>
-    <row r="909" ht="15.75" customHeight="1">
-      <c r="H909" s="2"/>
-      <c r="I909" s="2"/>
-      <c r="J909" s="3"/>
-      <c r="K909" s="4"/>
-      <c r="L909" s="2"/>
-      <c r="M909" s="5"/>
-      <c r="N909" s="6"/>
-    </row>
-    <row r="910" ht="15.75" customHeight="1">
-      <c r="H910" s="2"/>
-      <c r="I910" s="2"/>
-      <c r="J910" s="3"/>
-      <c r="K910" s="4"/>
-      <c r="L910" s="2"/>
-      <c r="M910" s="5"/>
-      <c r="N910" s="6"/>
-    </row>
-    <row r="911" ht="15.75" customHeight="1">
-      <c r="H911" s="2"/>
-      <c r="I911" s="2"/>
-      <c r="J911" s="3"/>
-      <c r="K911" s="4"/>
-      <c r="L911" s="2"/>
-      <c r="M911" s="5"/>
-      <c r="N911" s="6"/>
-    </row>
-    <row r="912" ht="15.75" customHeight="1">
-      <c r="H912" s="2"/>
-      <c r="I912" s="2"/>
-      <c r="J912" s="3"/>
-      <c r="K912" s="4"/>
-      <c r="L912" s="2"/>
-      <c r="M912" s="5"/>
-      <c r="N912" s="6"/>
-    </row>
-    <row r="913" ht="15.75" customHeight="1">
-      <c r="H913" s="2"/>
-      <c r="I913" s="2"/>
-      <c r="J913" s="3"/>
-      <c r="K913" s="4"/>
-      <c r="L913" s="2"/>
-      <c r="M913" s="5"/>
-      <c r="N913" s="6"/>
-    </row>
-    <row r="914" ht="15.75" customHeight="1">
-      <c r="H914" s="2"/>
-      <c r="I914" s="2"/>
-      <c r="J914" s="3"/>
-      <c r="K914" s="4"/>
-      <c r="L914" s="2"/>
-      <c r="M914" s="5"/>
-      <c r="N914" s="6"/>
-    </row>
-    <row r="915" ht="15.75" customHeight="1">
-      <c r="H915" s="2"/>
-      <c r="I915" s="2"/>
-      <c r="J915" s="3"/>
-      <c r="K915" s="4"/>
-      <c r="L915" s="2"/>
-      <c r="M915" s="5"/>
-      <c r="N915" s="6"/>
-    </row>
-    <row r="916" ht="15.75" customHeight="1">
-      <c r="H916" s="2"/>
-      <c r="I916" s="2"/>
-      <c r="J916" s="3"/>
-      <c r="K916" s="4"/>
-      <c r="L916" s="2"/>
-      <c r="M916" s="5"/>
-      <c r="N916" s="6"/>
-    </row>
-    <row r="917" ht="15.75" customHeight="1">
-      <c r="H917" s="2"/>
-      <c r="I917" s="2"/>
-      <c r="J917" s="3"/>
-      <c r="K917" s="4"/>
-      <c r="L917" s="2"/>
-      <c r="M917" s="5"/>
-      <c r="N917" s="6"/>
-    </row>
-    <row r="918" ht="15.75" customHeight="1">
-      <c r="H918" s="2"/>
-      <c r="I918" s="2"/>
-      <c r="J918" s="3"/>
-      <c r="K918" s="4"/>
-      <c r="L918" s="2"/>
-      <c r="M918" s="5"/>
-      <c r="N918" s="6"/>
-    </row>
-    <row r="919" ht="15.75" customHeight="1">
-      <c r="H919" s="2"/>
-      <c r="I919" s="2"/>
-      <c r="J919" s="3"/>
-      <c r="K919" s="4"/>
-      <c r="L919" s="2"/>
-      <c r="M919" s="5"/>
-      <c r="N919" s="6"/>
-    </row>
-    <row r="920" ht="15.75" customHeight="1">
-      <c r="H920" s="2"/>
-      <c r="I920" s="2"/>
-      <c r="J920" s="3"/>
-      <c r="K920" s="4"/>
-      <c r="L920" s="2"/>
-      <c r="M920" s="5"/>
-      <c r="N920" s="6"/>
-    </row>
-    <row r="921" ht="15.75" customHeight="1">
-      <c r="H921" s="2"/>
-      <c r="I921" s="2"/>
-      <c r="J921" s="3"/>
-      <c r="K921" s="4"/>
-      <c r="L921" s="2"/>
-      <c r="M921" s="5"/>
-      <c r="N921" s="6"/>
-    </row>
-    <row r="922" ht="15.75" customHeight="1">
-      <c r="H922" s="2"/>
-      <c r="I922" s="2"/>
-      <c r="J922" s="3"/>
-      <c r="K922" s="4"/>
-      <c r="L922" s="2"/>
-      <c r="M922" s="5"/>
-      <c r="N922" s="6"/>
-    </row>
-    <row r="923" ht="15.75" customHeight="1">
-      <c r="H923" s="2"/>
-      <c r="I923" s="2"/>
-      <c r="J923" s="3"/>
-      <c r="K923" s="4"/>
-      <c r="L923" s="2"/>
-      <c r="M923" s="5"/>
-      <c r="N923" s="6"/>
-    </row>
-    <row r="924" ht="15.75" customHeight="1">
-      <c r="H924" s="2"/>
-      <c r="I924" s="2"/>
-      <c r="J924" s="3"/>
-      <c r="K924" s="4"/>
-      <c r="L924" s="2"/>
-      <c r="M924" s="5"/>
-      <c r="N924" s="6"/>
-    </row>
-    <row r="925" ht="15.75" customHeight="1">
-      <c r="H925" s="2"/>
-      <c r="I925" s="2"/>
-      <c r="J925" s="3"/>
-      <c r="K925" s="4"/>
-      <c r="L925" s="2"/>
-      <c r="M925" s="5"/>
-      <c r="N925" s="6"/>
-    </row>
-    <row r="926" ht="15.75" customHeight="1">
-      <c r="H926" s="2"/>
-      <c r="I926" s="2"/>
-      <c r="J926" s="3"/>
-      <c r="K926" s="4"/>
-      <c r="L926" s="2"/>
-      <c r="M926" s="5"/>
-      <c r="N926" s="6"/>
-    </row>
-    <row r="927" ht="15.75" customHeight="1">
-      <c r="H927" s="2"/>
-      <c r="I927" s="2"/>
-      <c r="J927" s="3"/>
-      <c r="K927" s="4"/>
-      <c r="L927" s="2"/>
-      <c r="M927" s="5"/>
-      <c r="N927" s="6"/>
-    </row>
-    <row r="928" ht="15.75" customHeight="1">
-      <c r="H928" s="2"/>
-      <c r="I928" s="2"/>
-      <c r="J928" s="3"/>
-      <c r="K928" s="4"/>
-      <c r="L928" s="2"/>
-      <c r="M928" s="5"/>
-      <c r="N928" s="6"/>
-    </row>
-    <row r="929" ht="15.75" customHeight="1">
-      <c r="H929" s="2"/>
-      <c r="I929" s="2"/>
-      <c r="J929" s="3"/>
-      <c r="K929" s="4"/>
-      <c r="L929" s="2"/>
-      <c r="M929" s="5"/>
-      <c r="N929" s="6"/>
-    </row>
-    <row r="930" ht="15.75" customHeight="1">
-      <c r="H930" s="2"/>
-      <c r="I930" s="2"/>
-      <c r="J930" s="3"/>
-      <c r="K930" s="4"/>
-      <c r="L930" s="2"/>
-      <c r="M930" s="5"/>
-      <c r="N930" s="6"/>
-    </row>
-    <row r="931" ht="15.75" customHeight="1">
-      <c r="H931" s="2"/>
-      <c r="I931" s="2"/>
-      <c r="J931" s="3"/>
-      <c r="K931" s="4"/>
-      <c r="L931" s="2"/>
-      <c r="M931" s="5"/>
-      <c r="N931" s="6"/>
-    </row>
-    <row r="932" ht="15.75" customHeight="1">
-      <c r="H932" s="2"/>
-      <c r="I932" s="2"/>
-      <c r="J932" s="3"/>
-      <c r="K932" s="4"/>
-      <c r="L932" s="2"/>
-      <c r="M932" s="5"/>
-      <c r="N932" s="6"/>
-    </row>
-    <row r="933" ht="15.75" customHeight="1">
-      <c r="H933" s="2"/>
-      <c r="I933" s="2"/>
-      <c r="J933" s="3"/>
-      <c r="K933" s="4"/>
-      <c r="L933" s="2"/>
-      <c r="M933" s="5"/>
-      <c r="N933" s="6"/>
-    </row>
-    <row r="934" ht="15.75" customHeight="1">
-      <c r="H934" s="2"/>
-      <c r="I934" s="2"/>
-      <c r="J934" s="3"/>
-      <c r="K934" s="4"/>
-      <c r="L934" s="2"/>
-      <c r="M934" s="5"/>
-      <c r="N934" s="6"/>
-    </row>
-    <row r="935" ht="15.75" customHeight="1">
-      <c r="H935" s="2"/>
-      <c r="I935" s="2"/>
-      <c r="J935" s="3"/>
-      <c r="K935" s="4"/>
-      <c r="L935" s="2"/>
-      <c r="M935" s="5"/>
-      <c r="N935" s="6"/>
-    </row>
-    <row r="936" ht="15.75" customHeight="1">
-      <c r="H936" s="2"/>
-      <c r="I936" s="2"/>
-      <c r="J936" s="3"/>
-      <c r="K936" s="4"/>
-      <c r="L936" s="2"/>
-      <c r="M936" s="5"/>
-      <c r="N936" s="6"/>
-    </row>
-    <row r="937" ht="15.75" customHeight="1">
-      <c r="H937" s="2"/>
-      <c r="I937" s="2"/>
-      <c r="J937" s="3"/>
-      <c r="K937" s="4"/>
-      <c r="L937" s="2"/>
-      <c r="M937" s="5"/>
-      <c r="N937" s="6"/>
-    </row>
-    <row r="938" ht="15.75" customHeight="1">
-      <c r="H938" s="2"/>
-      <c r="I938" s="2"/>
-      <c r="J938" s="3"/>
-      <c r="K938" s="4"/>
-      <c r="L938" s="2"/>
-      <c r="M938" s="5"/>
-      <c r="N938" s="6"/>
-    </row>
-    <row r="939" ht="15.75" customHeight="1">
-      <c r="H939" s="2"/>
-      <c r="I939" s="2"/>
-      <c r="J939" s="3"/>
-      <c r="K939" s="4"/>
-      <c r="L939" s="2"/>
-      <c r="M939" s="5"/>
-      <c r="N939" s="6"/>
-    </row>
-    <row r="940" ht="15.75" customHeight="1">
-      <c r="H940" s="2"/>
-      <c r="I940" s="2"/>
-      <c r="J940" s="3"/>
-      <c r="K940" s="4"/>
-      <c r="L940" s="2"/>
-      <c r="M940" s="5"/>
-      <c r="N940" s="6"/>
-    </row>
-    <row r="941" ht="15.75" customHeight="1">
-      <c r="H941" s="2"/>
-      <c r="I941" s="2"/>
-      <c r="J941" s="3"/>
-      <c r="K941" s="4"/>
-      <c r="L941" s="2"/>
-      <c r="M941" s="5"/>
-      <c r="N941" s="6"/>
-    </row>
-    <row r="942" ht="15.75" customHeight="1">
-      <c r="H942" s="2"/>
-      <c r="I942" s="2"/>
-      <c r="J942" s="3"/>
-      <c r="K942" s="4"/>
-      <c r="L942" s="2"/>
-      <c r="M942" s="5"/>
-      <c r="N942" s="6"/>
-    </row>
-    <row r="943" ht="15.75" customHeight="1">
-      <c r="H943" s="2"/>
-      <c r="I943" s="2"/>
-      <c r="J943" s="3"/>
-      <c r="K943" s="4"/>
-      <c r="L943" s="2"/>
-      <c r="M943" s="5"/>
-      <c r="N943" s="6"/>
-    </row>
-    <row r="944" ht="15.75" customHeight="1">
-      <c r="H944" s="2"/>
-      <c r="I944" s="2"/>
-      <c r="J944" s="3"/>
-      <c r="K944" s="4"/>
-      <c r="L944" s="2"/>
-      <c r="M944" s="5"/>
-      <c r="N944" s="6"/>
-    </row>
-    <row r="945" ht="15.75" customHeight="1">
-      <c r="H945" s="2"/>
-      <c r="I945" s="2"/>
-      <c r="J945" s="3"/>
-      <c r="K945" s="4"/>
-      <c r="L945" s="2"/>
-      <c r="M945" s="5"/>
-      <c r="N945" s="6"/>
-    </row>
-    <row r="946" ht="15.75" customHeight="1">
-      <c r="H946" s="2"/>
-      <c r="I946" s="2"/>
-      <c r="J946" s="3"/>
-      <c r="K946" s="4"/>
-      <c r="L946" s="2"/>
-      <c r="M946" s="5"/>
-      <c r="N946" s="6"/>
-    </row>
-    <row r="947" ht="15.75" customHeight="1">
-      <c r="H947" s="2"/>
-      <c r="I947" s="2"/>
-      <c r="J947" s="3"/>
-      <c r="K947" s="4"/>
-      <c r="L947" s="2"/>
-      <c r="M947" s="5"/>
-      <c r="N947" s="6"/>
-    </row>
-    <row r="948" ht="15.75" customHeight="1">
-      <c r="H948" s="2"/>
-      <c r="I948" s="2"/>
-      <c r="J948" s="3"/>
-      <c r="K948" s="4"/>
-      <c r="L948" s="2"/>
-      <c r="M948" s="5"/>
-      <c r="N948" s="6"/>
-    </row>
-    <row r="949" ht="15.75" customHeight="1">
-      <c r="H949" s="2"/>
-      <c r="I949" s="2"/>
-      <c r="J949" s="3"/>
-      <c r="K949" s="4"/>
-      <c r="L949" s="2"/>
-      <c r="M949" s="5"/>
-      <c r="N949" s="6"/>
-    </row>
-    <row r="950" ht="15.75" customHeight="1">
-      <c r="H950" s="2"/>
-      <c r="I950" s="2"/>
-      <c r="J950" s="3"/>
-      <c r="K950" s="4"/>
-      <c r="L950" s="2"/>
-      <c r="M950" s="5"/>
-      <c r="N950" s="6"/>
-    </row>
-    <row r="951" ht="15.75" customHeight="1">
-      <c r="H951" s="2"/>
-      <c r="I951" s="2"/>
-      <c r="J951" s="3"/>
-      <c r="K951" s="4"/>
-      <c r="L951" s="2"/>
-      <c r="M951" s="5"/>
-      <c r="N951" s="6"/>
-    </row>
-    <row r="952" ht="15.75" customHeight="1">
-      <c r="H952" s="2"/>
-      <c r="I952" s="2"/>
-      <c r="J952" s="3"/>
-      <c r="K952" s="4"/>
-      <c r="L952" s="2"/>
-      <c r="M952" s="5"/>
-      <c r="N952" s="6"/>
-    </row>
-    <row r="953" ht="15.75" customHeight="1">
-      <c r="H953" s="2"/>
-      <c r="I953" s="2"/>
-      <c r="J953" s="3"/>
-      <c r="K953" s="4"/>
-      <c r="L953" s="2"/>
-      <c r="M953" s="5"/>
-      <c r="N953" s="6"/>
-    </row>
-    <row r="954" ht="15.75" customHeight="1">
-      <c r="H954" s="2"/>
-      <c r="I954" s="2"/>
-      <c r="J954" s="3"/>
-      <c r="K954" s="4"/>
-      <c r="L954" s="2"/>
-      <c r="M954" s="5"/>
-      <c r="N954" s="6"/>
-    </row>
-    <row r="955" ht="15.75" customHeight="1">
-      <c r="H955" s="2"/>
-      <c r="I955" s="2"/>
-      <c r="J955" s="3"/>
-      <c r="K955" s="4"/>
-      <c r="L955" s="2"/>
-      <c r="M955" s="5"/>
-      <c r="N955" s="6"/>
-    </row>
-    <row r="956" ht="15.75" customHeight="1">
-      <c r="H956" s="2"/>
-      <c r="I956" s="2"/>
-      <c r="J956" s="3"/>
-      <c r="K956" s="4"/>
-      <c r="L956" s="2"/>
-      <c r="M956" s="5"/>
-      <c r="N956" s="6"/>
-    </row>
-    <row r="957" ht="15.75" customHeight="1">
-      <c r="H957" s="2"/>
-      <c r="I957" s="2"/>
-      <c r="J957" s="3"/>
-      <c r="K957" s="4"/>
-      <c r="L957" s="2"/>
-      <c r="M957" s="5"/>
-      <c r="N957" s="6"/>
-    </row>
-    <row r="958" ht="15.75" customHeight="1">
-      <c r="H958" s="2"/>
-      <c r="I958" s="2"/>
-      <c r="J958" s="3"/>
-      <c r="K958" s="4"/>
-      <c r="L958" s="2"/>
-      <c r="M958" s="5"/>
-      <c r="N958" s="6"/>
-    </row>
-    <row r="959" ht="15.75" customHeight="1">
-      <c r="H959" s="2"/>
-      <c r="I959" s="2"/>
-      <c r="J959" s="3"/>
-      <c r="K959" s="4"/>
-      <c r="L959" s="2"/>
-      <c r="M959" s="5"/>
-      <c r="N959" s="6"/>
-    </row>
-    <row r="960" ht="15.75" customHeight="1">
-      <c r="H960" s="2"/>
-      <c r="I960" s="2"/>
-      <c r="J960" s="3"/>
-      <c r="K960" s="4"/>
-      <c r="L960" s="2"/>
-      <c r="M960" s="5"/>
-      <c r="N960" s="6"/>
-    </row>
-    <row r="961" ht="15.75" customHeight="1">
-      <c r="H961" s="2"/>
-      <c r="I961" s="2"/>
-      <c r="J961" s="3"/>
-      <c r="K961" s="4"/>
-      <c r="L961" s="2"/>
-      <c r="M961" s="5"/>
-      <c r="N961" s="6"/>
-    </row>
-    <row r="962" ht="15.75" customHeight="1">
-      <c r="H962" s="2"/>
-      <c r="I962" s="2"/>
-      <c r="J962" s="3"/>
-      <c r="K962" s="4"/>
-      <c r="L962" s="2"/>
-      <c r="M962" s="5"/>
-      <c r="N962" s="6"/>
-    </row>
-    <row r="963" ht="15.75" customHeight="1">
-      <c r="H963" s="2"/>
-      <c r="I963" s="2"/>
-      <c r="J963" s="3"/>
-      <c r="K963" s="4"/>
-      <c r="L963" s="2"/>
-      <c r="M963" s="5"/>
-      <c r="N963" s="6"/>
-    </row>
-    <row r="964" ht="15.75" customHeight="1">
-      <c r="H964" s="2"/>
-      <c r="I964" s="2"/>
-      <c r="J964" s="3"/>
-      <c r="K964" s="4"/>
-      <c r="L964" s="2"/>
-      <c r="M964" s="5"/>
-      <c r="N964" s="6"/>
-    </row>
-    <row r="965" ht="15.75" customHeight="1">
-      <c r="H965" s="2"/>
-      <c r="I965" s="2"/>
-      <c r="J965" s="3"/>
-      <c r="K965" s="4"/>
-      <c r="L965" s="2"/>
-      <c r="M965" s="5"/>
-      <c r="N965" s="6"/>
-    </row>
-    <row r="966" ht="15.75" customHeight="1">
-      <c r="H966" s="2"/>
-      <c r="I966" s="2"/>
-      <c r="J966" s="3"/>
-      <c r="K966" s="4"/>
-      <c r="L966" s="2"/>
-      <c r="M966" s="5"/>
-      <c r="N966" s="6"/>
-    </row>
-    <row r="967" ht="15.75" customHeight="1">
-      <c r="H967" s="2"/>
-      <c r="I967" s="2"/>
-      <c r="J967" s="3"/>
-      <c r="K967" s="4"/>
-      <c r="L967" s="2"/>
-      <c r="M967" s="5"/>
-      <c r="N967" s="6"/>
-    </row>
-    <row r="968" ht="15.75" customHeight="1">
-      <c r="H968" s="2"/>
-      <c r="I968" s="2"/>
-      <c r="J968" s="3"/>
-      <c r="K968" s="4"/>
-      <c r="L968" s="2"/>
-      <c r="M968" s="5"/>
-      <c r="N968" s="6"/>
-    </row>
-    <row r="969" ht="15.75" customHeight="1">
-      <c r="H969" s="2"/>
-      <c r="I969" s="2"/>
-      <c r="J969" s="3"/>
-      <c r="K969" s="4"/>
-      <c r="L969" s="2"/>
-      <c r="M969" s="5"/>
-      <c r="N969" s="6"/>
-    </row>
-    <row r="970" ht="15.75" customHeight="1">
-      <c r="H970" s="2"/>
-      <c r="I970" s="2"/>
-      <c r="J970" s="3"/>
-      <c r="K970" s="4"/>
-      <c r="L970" s="2"/>
-      <c r="M970" s="5"/>
-      <c r="N970" s="6"/>
-    </row>
-    <row r="971" ht="15.75" customHeight="1">
-      <c r="H971" s="2"/>
-      <c r="I971" s="2"/>
-      <c r="J971" s="3"/>
-      <c r="K971" s="4"/>
-      <c r="L971" s="2"/>
-      <c r="M971" s="5"/>
-      <c r="N971" s="6"/>
-    </row>
-    <row r="972" ht="15.75" customHeight="1">
-      <c r="H972" s="2"/>
-      <c r="I972" s="2"/>
-      <c r="J972" s="3"/>
-      <c r="K972" s="4"/>
-      <c r="L972" s="2"/>
-      <c r="M972" s="5"/>
-      <c r="N972" s="6"/>
-    </row>
-    <row r="973" ht="15.75" customHeight="1">
-      <c r="H973" s="2"/>
-      <c r="I973" s="2"/>
-      <c r="J973" s="3"/>
-      <c r="K973" s="4"/>
-      <c r="L973" s="2"/>
-      <c r="M973" s="5"/>
-      <c r="N973" s="6"/>
-    </row>
-    <row r="974" ht="15.75" customHeight="1">
-      <c r="H974" s="2"/>
-      <c r="I974" s="2"/>
-      <c r="J974" s="3"/>
-      <c r="K974" s="4"/>
-      <c r="L974" s="2"/>
-      <c r="M974" s="5"/>
-      <c r="N974" s="6"/>
-    </row>
-    <row r="975" ht="15.75" customHeight="1">
-      <c r="H975" s="2"/>
-      <c r="I975" s="2"/>
-      <c r="J975" s="3"/>
-      <c r="K975" s="4"/>
-      <c r="L975" s="2"/>
-      <c r="M975" s="5"/>
-      <c r="N975" s="6"/>
-    </row>
-    <row r="976" ht="15.75" customHeight="1">
-      <c r="H976" s="2"/>
-      <c r="I976" s="2"/>
-      <c r="J976" s="3"/>
-      <c r="K976" s="4"/>
-      <c r="L976" s="2"/>
-      <c r="M976" s="5"/>
-      <c r="N976" s="6"/>
-    </row>
-    <row r="977" ht="15.75" customHeight="1">
-      <c r="H977" s="2"/>
-      <c r="I977" s="2"/>
-      <c r="J977" s="3"/>
-      <c r="K977" s="4"/>
-      <c r="L977" s="2"/>
-      <c r="M977" s="5"/>
-      <c r="N977" s="6"/>
-    </row>
-    <row r="978" ht="15.75" customHeight="1">
-      <c r="H978" s="2"/>
-      <c r="I978" s="2"/>
-      <c r="J978" s="3"/>
-      <c r="K978" s="4"/>
-      <c r="L978" s="2"/>
-      <c r="M978" s="5"/>
-      <c r="N978" s="6"/>
-    </row>
-    <row r="979" ht="15.75" customHeight="1">
-      <c r="H979" s="2"/>
-      <c r="I979" s="2"/>
-      <c r="J979" s="3"/>
-      <c r="K979" s="4"/>
-      <c r="L979" s="2"/>
-      <c r="M979" s="5"/>
-      <c r="N979" s="6"/>
-    </row>
-    <row r="980" ht="15.75" customHeight="1">
-      <c r="H980" s="2"/>
-      <c r="I980" s="2"/>
-      <c r="J980" s="3"/>
-      <c r="K980" s="4"/>
-      <c r="L980" s="2"/>
-      <c r="M980" s="5"/>
-      <c r="N980" s="6"/>
-    </row>
-    <row r="981" ht="15.75" customHeight="1">
-      <c r="H981" s="2"/>
-      <c r="I981" s="2"/>
-      <c r="J981" s="3"/>
-      <c r="K981" s="4"/>
-      <c r="L981" s="2"/>
-      <c r="M981" s="5"/>
-      <c r="N981" s="6"/>
-    </row>
-    <row r="982" ht="15.75" customHeight="1">
-      <c r="H982" s="2"/>
-      <c r="I982" s="2"/>
-      <c r="J982" s="3"/>
-      <c r="K982" s="4"/>
-      <c r="L982" s="2"/>
-      <c r="M982" s="5"/>
-      <c r="N982" s="6"/>
-    </row>
-    <row r="983" ht="15.75" customHeight="1">
-      <c r="H983" s="2"/>
-      <c r="I983" s="2"/>
-      <c r="J983" s="3"/>
-      <c r="K983" s="4"/>
-      <c r="L983" s="2"/>
-      <c r="M983" s="5"/>
-      <c r="N983" s="6"/>
-    </row>
-    <row r="984" ht="15.75" customHeight="1">
-      <c r="H984" s="2"/>
-      <c r="I984" s="2"/>
-      <c r="J984" s="3"/>
-      <c r="K984" s="4"/>
-      <c r="L984" s="2"/>
-      <c r="M984" s="5"/>
-      <c r="N984" s="6"/>
-    </row>
-    <row r="985" ht="15.75" customHeight="1">
-      <c r="H985" s="2"/>
-      <c r="I985" s="2"/>
-      <c r="J985" s="3"/>
-      <c r="K985" s="4"/>
-      <c r="L985" s="2"/>
-      <c r="M985" s="5"/>
-      <c r="N985" s="6"/>
-    </row>
-    <row r="986" ht="15.75" customHeight="1">
-      <c r="H986" s="2"/>
-      <c r="I986" s="2"/>
-      <c r="J986" s="3"/>
-      <c r="K986" s="4"/>
-      <c r="L986" s="2"/>
-      <c r="M986" s="5"/>
-      <c r="N986" s="6"/>
-    </row>
-    <row r="987" ht="15.75" customHeight="1">
-      <c r="H987" s="2"/>
-      <c r="I987" s="2"/>
-      <c r="J987" s="3"/>
-      <c r="K987" s="4"/>
-      <c r="L987" s="2"/>
-      <c r="M987" s="5"/>
-      <c r="N987" s="6"/>
-    </row>
-    <row r="988" ht="15.75" customHeight="1">
-      <c r="H988" s="2"/>
-      <c r="I988" s="2"/>
-      <c r="J988" s="3"/>
-      <c r="K988" s="4"/>
-      <c r="L988" s="2"/>
-      <c r="M988" s="5"/>
-      <c r="N988" s="6"/>
-    </row>
-    <row r="989" ht="15.75" customHeight="1">
-      <c r="H989" s="2"/>
-      <c r="I989" s="2"/>
-      <c r="J989" s="3"/>
-      <c r="K989" s="4"/>
-      <c r="L989" s="2"/>
-      <c r="M989" s="5"/>
-      <c r="N989" s="6"/>
-    </row>
-    <row r="990" ht="15.75" customHeight="1">
-      <c r="H990" s="2"/>
-      <c r="I990" s="2"/>
-      <c r="J990" s="3"/>
-      <c r="K990" s="4"/>
-      <c r="L990" s="2"/>
-      <c r="M990" s="5"/>
-      <c r="N990" s="6"/>
-    </row>
-    <row r="991" ht="15.75" customHeight="1">
-      <c r="H991" s="2"/>
-      <c r="I991" s="2"/>
-      <c r="J991" s="3"/>
-      <c r="K991" s="4"/>
-      <c r="L991" s="2"/>
-      <c r="M991" s="5"/>
-      <c r="N991" s="6"/>
-    </row>
-    <row r="992" ht="15.75" customHeight="1">
-      <c r="H992" s="2"/>
-      <c r="I992" s="2"/>
-      <c r="J992" s="3"/>
-      <c r="K992" s="4"/>
-      <c r="L992" s="2"/>
-      <c r="M992" s="5"/>
-      <c r="N992" s="6"/>
-    </row>
-    <row r="993" ht="15.75" customHeight="1">
-      <c r="H993" s="2"/>
-      <c r="I993" s="2"/>
-      <c r="J993" s="3"/>
-      <c r="K993" s="4"/>
-      <c r="L993" s="2"/>
-      <c r="M993" s="5"/>
-      <c r="N993" s="6"/>
-    </row>
-    <row r="994" ht="15.75" customHeight="1">
-      <c r="H994" s="2"/>
-      <c r="I994" s="2"/>
-      <c r="J994" s="3"/>
-      <c r="K994" s="4"/>
-      <c r="L994" s="2"/>
-      <c r="M994" s="5"/>
-      <c r="N994" s="6"/>
-    </row>
-    <row r="995" ht="15.75" customHeight="1">
-      <c r="H995" s="2"/>
-      <c r="I995" s="2"/>
-      <c r="J995" s="3"/>
-      <c r="K995" s="4"/>
-      <c r="L995" s="2"/>
-      <c r="M995" s="5"/>
-      <c r="N995" s="6"/>
-    </row>
-    <row r="996" ht="15.75" customHeight="1">
-      <c r="H996" s="2"/>
-      <c r="I996" s="2"/>
-      <c r="J996" s="3"/>
-      <c r="K996" s="4"/>
-      <c r="L996" s="2"/>
-      <c r="M996" s="5"/>
-      <c r="N996" s="6"/>
-    </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="H997" s="2"/>
-      <c r="I997" s="2"/>
-      <c r="J997" s="3"/>
-      <c r="K997" s="4"/>
-      <c r="L997" s="2"/>
-      <c r="M997" s="5"/>
-      <c r="N997" s="6"/>
-    </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="H998" s="2"/>
-      <c r="I998" s="2"/>
-      <c r="J998" s="3"/>
-      <c r="K998" s="4"/>
-      <c r="L998" s="2"/>
-      <c r="M998" s="5"/>
-      <c r="N998" s="6"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="H999" s="2"/>
-      <c r="I999" s="2"/>
-      <c r="J999" s="3"/>
-      <c r="K999" s="4"/>
-      <c r="L999" s="2"/>
-      <c r="M999" s="5"/>
-      <c r="N999" s="6"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="H1000" s="2"/>
-      <c r="I1000" s="2"/>
-      <c r="J1000" s="3"/>
-      <c r="K1000" s="4"/>
-      <c r="L1000" s="2"/>
-      <c r="M1000" s="5"/>
-      <c r="N1000" s="6"/>
-    </row>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F2"/>
@@ -25714,14 +22752,11 @@
     <hyperlink r:id="rId426" ref="F441"/>
     <hyperlink r:id="rId427" ref="F442"/>
     <hyperlink r:id="rId428" ref="F443"/>
-    <hyperlink r:id="rId429" ref="F444"/>
-    <hyperlink r:id="rId430" ref="F445"/>
-    <hyperlink r:id="rId431" ref="F446"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId432"/>
+  <drawing r:id="rId429"/>
 </worksheet>
 </file>
 
@@ -25732,7 +22767,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -26730,7 +23765,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="21" ht="15.75" customHeight="1"/>
